--- a/planning/Pre_Day_1_Portal_Alignment_Planner.xlsx
+++ b/planning/Pre_Day_1_Portal_Alignment_Planner.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consideration (next)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Portal Map'!$A$4:$N$163</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Alignment &amp; Gaps'!$A$4:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Portal Map'!$A$4:$N$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Alignment &amp; Gaps'!$A$4:$K$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pre-Day 1 Documents'!$A$4:$H$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -130,6 +130,21 @@
       <color rgb="00411980"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002A8346"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00AD050C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="008A5A00"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -210,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -257,13 +272,22 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -732,7 +756,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Every screen, tab, section and field in the v3 mockups, both sides. Use the Status column to see where each element stands, and the Connects to column to see which elements cross between the two portals.</t>
+          <t>Every screen, tab, section and field in the mockups, both sides, after the gap-closing pass. Use the Status column to see where each element stands, and the Connects to column to see which elements cross between the two portals.</t>
         </is>
       </c>
     </row>
@@ -744,7 +768,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>The comparison. One row per finding, with what the mockup does, what the source says, a verdict and the action. Sort by Priority to get the working list.</t>
+          <t>The comparison. One row per finding, with what the mockup does, what the source says, a verdict, the action, and what the mockups were changed to do about it. Sort by Priority to get the working list.</t>
         </is>
       </c>
     </row>
@@ -936,7 +960,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>New Hire portal mockup (v3) and Hiring Manager portal mockup (v3), sharing one state so cross-portal handoffs are real. 74-entry assumption register: 47 new hire, 18 manager, 9 connection.</t>
+          <t>New Hire portal mockup (v3) and Hiring Manager portal mockup (v3), sharing one state so cross-portal handoffs are real. 82-entry assumption register: 50 new hire, 21 manager, 11 connection, 2 retired. Eleven cross-portal handoffs.</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N173"/>
+  <dimension ref="A1:N189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1608,7 +1632,7 @@
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>First in list, earliest due. No gate exists today.</t>
+          <t>Earliest of the provisioning tasks. No gate exists today.</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
@@ -2812,7 +2836,7 @@
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>Background check — status only</t>
+          <t>Tax forms and withholding</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -2827,17 +2851,17 @@
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>First Advantage</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>Status only, no action.</t>
+          <t>Replaced the passive background-check card, which is now a real task.</t>
         </is>
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>HM H-00 third-party</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L27" s="10" t="inlineStr">
@@ -2847,7 +2871,7 @@
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
-          <t>Future State Seq 3</t>
+          <t>Merge Analysis 8</t>
         </is>
       </c>
       <c r="N27" s="13" t="inlineStr">
@@ -5399,17 +5423,17 @@
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Contact preferences</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>Preferred language</t>
+          <t>Preferred channel (email / text / either)</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
@@ -5419,32 +5443,32 @@
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>Country of hire</t>
+          <t>Blank</t>
         </is>
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>Drives which language policy documents are served.</t>
+          <t>Named in the source with no definition.</t>
         </is>
       </c>
       <c r="K63" s="10" t="inlineStr">
         <is>
-          <t>P-05 documents</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L63" s="10" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>A-05</t>
         </is>
       </c>
       <c r="M63" s="10" t="inlineStr">
         <is>
-          <t>NH OI-16</t>
-        </is>
-      </c>
-      <c r="N63" s="16" t="inlineStr">
-        <is>
-          <t>CONFLICT — see Alignment G-02</t>
+          <t>NH OI-18</t>
+        </is>
+      </c>
+      <c r="N63" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5476,27 +5500,27 @@
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>Preferred channel (email / text / either)</t>
+          <t>Opt-in for non-essential updates</t>
         </is>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="H64" s="12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I64" s="12" t="inlineStr">
         <is>
-          <t>Blank</t>
+          <t>Unchecked</t>
         </is>
       </c>
       <c r="J64" s="12" t="inlineStr">
         <is>
-          <t>Named in the source with no definition.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K64" s="12" t="inlineStr">
@@ -5543,17 +5567,17 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>Contact preferences</t>
+          <t>Adjustments</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>Opt-in for non-essential updates</t>
+          <t>Workplace adjustments free text</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Multi line text</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
@@ -5563,32 +5587,32 @@
       </c>
       <c r="I65" s="10" t="inlineStr">
         <is>
-          <t>Unchecked</t>
+          <t>Blank</t>
         </is>
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Always visible, never demanded.</t>
         </is>
       </c>
       <c r="K65" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Equipment screen link</t>
         </is>
       </c>
       <c r="L65" s="10" t="inlineStr">
         <is>
-          <t>A-05</t>
+          <t>A-06</t>
         </is>
       </c>
       <c r="M65" s="10" t="inlineStr">
         <is>
-          <t>NH OI-18</t>
-        </is>
-      </c>
-      <c r="N65" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>BTR accommodation capture</t>
+        </is>
+      </c>
+      <c r="N65" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -5620,12 +5644,12 @@
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
-          <t>Workplace adjustments free text</t>
+          <t>'I'd rather discuss this privately' route</t>
         </is>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>Multi line text</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="H66" s="12" t="inlineStr">
@@ -5635,17 +5659,17 @@
       </c>
       <c r="I66" s="12" t="inlineStr">
         <is>
-          <t>Blank</t>
+          <t>Unchecked</t>
         </is>
       </c>
       <c r="J66" s="12" t="inlineStr">
         <is>
-          <t>Always visible, never demanded.</t>
+          <t>Routes to PEX; disables and clears the text field so nothing is stored.</t>
         </is>
       </c>
       <c r="K66" s="12" t="inlineStr">
         <is>
-          <t>Equipment screen link</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L66" s="12" t="inlineStr">
@@ -5655,7 +5679,7 @@
       </c>
       <c r="M66" s="12" t="inlineStr">
         <is>
-          <t>BTR accommodation capture</t>
+          <t>NH OI-23</t>
         </is>
       </c>
       <c r="N66" s="13" t="inlineStr">
@@ -5687,17 +5711,17 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>Adjustments</t>
+          <t>Self-ID</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>'I'd rather discuss this privately' route</t>
+          <t>Voluntary self-identification (collapsed by default)</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Container</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
@@ -5707,32 +5731,32 @@
       </c>
       <c r="I67" s="10" t="inlineStr">
         <is>
-          <t>Unchecked</t>
+          <t>Blank</t>
         </is>
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>Routes to PEX; disables and clears the text field so nothing is stored.</t>
+          <t>Four categories, every one with 'prefer not to say'. Paired with its privacy notice.</t>
         </is>
       </c>
       <c r="K67" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P-05 Self-ID notice</t>
         </is>
       </c>
       <c r="L67" s="10" t="inlineStr">
         <is>
-          <t>A-06</t>
+          <t>A-07</t>
         </is>
       </c>
       <c r="M67" s="10" t="inlineStr">
         <is>
-          <t>NH OI-23</t>
-        </is>
-      </c>
-      <c r="N67" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>NH OI-22</t>
+        </is>
+      </c>
+      <c r="N67" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5759,52 +5783,52 @@
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>Self-ID</t>
+          <t>Boundary</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
         <is>
-          <t>Voluntary self-identification (collapsed by default)</t>
+          <t>Banking and direct deposit — locked card</t>
         </is>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
-          <t>Container</t>
+          <t>Boundary card</t>
         </is>
       </c>
       <c r="H68" s="12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I68" s="12" t="inlineStr">
         <is>
-          <t>Blank</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J68" s="12" t="inlineStr">
         <is>
-          <t>Four categories, every one with 'prefer not to say'. Paired with its privacy notice.</t>
+          <t>Explains why it is elsewhere. Names tax, swag and dietary as deliberate exclusions too.</t>
         </is>
       </c>
       <c r="K68" s="12" t="inlineStr">
         <is>
-          <t>P-05 Self-ID notice</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L68" s="12" t="inlineStr">
         <is>
-          <t>A-07</t>
+          <t>A-10 / A-11</t>
         </is>
       </c>
       <c r="M68" s="12" t="inlineStr">
         <is>
-          <t>NH OI-22</t>
-        </is>
-      </c>
-      <c r="N68" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>Merge Analysis 3</t>
+        </is>
+      </c>
+      <c r="N68" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -5816,12 +5840,12 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>P-01c</t>
+          <t>P-01</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Personal details — Tab 3 Preferences</t>
+          <t>Personal details — behaviour</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
@@ -5831,17 +5855,17 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>Boundary</t>
+          <t>Behaviour</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>Banking and direct deposit — locked card</t>
+          <t>Autosave draft with visible saved state</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>Boundary card</t>
+          <t>Behaviour</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
@@ -5856,7 +5880,7 @@
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>Explains why it is elsewhere. Names tax, swag and dietary as deliberate exclusions too.</t>
+          <t>Survives leaving and returning.</t>
         </is>
       </c>
       <c r="K69" s="10" t="inlineStr">
@@ -5866,12 +5890,12 @@
       </c>
       <c r="L69" s="10" t="inlineStr">
         <is>
-          <t>A-10 / A-11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M69" s="10" t="inlineStr">
         <is>
-          <t>Merge Analysis 3</t>
+          <t>PRD S2-US02</t>
         </is>
       </c>
       <c r="N69" s="13" t="inlineStr">
@@ -5908,7 +5932,7 @@
       </c>
       <c r="F70" s="12" t="inlineStr">
         <is>
-          <t>Autosave draft with visible saved state</t>
+          <t>Inline validation on blur; per-tab completion counts</t>
         </is>
       </c>
       <c r="G70" s="12" t="inlineStr">
@@ -5928,7 +5952,7 @@
       </c>
       <c r="J70" s="12" t="inlineStr">
         <is>
-          <t>Survives leaving and returning.</t>
+          <t>Never browser alerts. Submit names what is missing.</t>
         </is>
       </c>
       <c r="K70" s="12" t="inlineStr">
@@ -5960,32 +5984,32 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>P-01</t>
+          <t>P-02</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Personal details — behaviour</t>
+          <t>Review your job description</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>#/details</t>
+          <t>#/jd</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>Behaviour</t>
+          <t>Role summary</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>Inline validation on blur; per-tab completion counts</t>
+          <t>Title, department, reports to, location + arrangement, employment type, start date</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>Behaviour</t>
+          <t>Read-only ×6</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
@@ -5995,17 +6019,17 @@
       </c>
       <c r="I71" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Workday requisition</t>
         </is>
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>Never browser alerts. Submit names what is missing.</t>
+          <t>Labelled as coming from the official record.</t>
         </is>
       </c>
       <c r="K71" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HM sees the same record</t>
         </is>
       </c>
       <c r="L71" s="10" t="inlineStr">
@@ -6015,7 +6039,7 @@
       </c>
       <c r="M71" s="10" t="inlineStr">
         <is>
-          <t>PRD S2-US02</t>
+          <t>NH Fields P-02.1-6</t>
         </is>
       </c>
       <c r="N71" s="13" t="inlineStr">
@@ -6052,12 +6076,12 @@
       </c>
       <c r="F72" s="12" t="inlineStr">
         <is>
-          <t>Title, department, reports to, location + arrangement, employment type, start date</t>
+          <t>No compensation — 'in your signed offer letter'</t>
         </is>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>Read-only ×6</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H72" s="12" t="inlineStr">
@@ -6067,32 +6091,32 @@
       </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
-          <t>Workday requisition</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J72" s="12" t="inlineStr">
         <is>
-          <t>Labelled as coming from the official record.</t>
+          <t>Deliberate omission; page is manager-visible.</t>
         </is>
       </c>
       <c r="K72" s="12" t="inlineStr">
         <is>
-          <t>HM sees the same record</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L72" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A-12</t>
         </is>
       </c>
       <c r="M72" s="12" t="inlineStr">
         <is>
-          <t>NH Fields P-02.1-6</t>
-        </is>
-      </c>
-      <c r="N72" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>NH OI-10</t>
+        </is>
+      </c>
+      <c r="N72" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6119,17 +6143,17 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>Role summary</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>No compensation — 'in your signed offer letter'</t>
+          <t>Job description text, scrollable, placeholder-marked</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Read-only</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
@@ -6139,12 +6163,12 @@
       </c>
       <c r="I73" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>Deliberate omission; page is manager-visible.</t>
+          <t>Scroll to end gates the acknowledgement.</t>
         </is>
       </c>
       <c r="K73" s="10" t="inlineStr">
@@ -6154,17 +6178,17 @@
       </c>
       <c r="L73" s="10" t="inlineStr">
         <is>
-          <t>A-12</t>
+          <t>A-13 / A-24</t>
         </is>
       </c>
       <c r="M73" s="10" t="inlineStr">
         <is>
-          <t>NH OI-10</t>
+          <t>NH Fields P-02.8</t>
         </is>
       </c>
       <c r="N73" s="15" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Open — content needed</t>
         </is>
       </c>
     </row>
@@ -6196,17 +6220,17 @@
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
-          <t>Job description text, scrollable, placeholder-marked</t>
+          <t>Link to the official system (internal-system treatment)</t>
         </is>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
-          <t>Read-only</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I74" s="12" t="inlineStr">
@@ -6216,7 +6240,7 @@
       </c>
       <c r="J74" s="12" t="inlineStr">
         <is>
-          <t>Scroll to end gates the acknowledgement.</t>
+          <t>Reads as another Equinix system, not the open internet.</t>
         </is>
       </c>
       <c r="K74" s="12" t="inlineStr">
@@ -6226,17 +6250,17 @@
       </c>
       <c r="L74" s="12" t="inlineStr">
         <is>
-          <t>A-13 / A-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M74" s="12" t="inlineStr">
         <is>
-          <t>NH Fields P-02.8</t>
-        </is>
-      </c>
-      <c r="N74" s="15" t="inlineStr">
-        <is>
-          <t>Open — content needed</t>
+          <t>Artifacts Served</t>
+        </is>
+      </c>
+      <c r="N74" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -6263,52 +6287,52 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>Link to the official system (internal-system treatment)</t>
+          <t>Three-level team view (manager, you, peers)</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>Link</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Workday org data</t>
         </is>
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>Reads as another Equinix system, not the open internet.</t>
+          <t>Explicitly not the suggested network; cross-links to it.</t>
         </is>
       </c>
       <c r="K75" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NH network screen</t>
         </is>
       </c>
       <c r="L75" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A-13</t>
         </is>
       </c>
       <c r="M75" s="10" t="inlineStr">
         <is>
-          <t>Artifacts Served</t>
-        </is>
-      </c>
-      <c r="N75" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>NH OI (org chart)</t>
+        </is>
+      </c>
+      <c r="N75" s="15" t="inlineStr">
+        <is>
+          <t>Open — delivery undefined</t>
         </is>
       </c>
     </row>
@@ -6335,52 +6359,52 @@
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Confirmation</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
-          <t>Three-level team view (manager, you, peers)</t>
+          <t>'I've read my job description and confirm…'</t>
         </is>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I76" s="12" t="inlineStr">
         <is>
-          <t>Workday org data</t>
+          <t>Unchecked</t>
         </is>
       </c>
       <c r="J76" s="12" t="inlineStr">
         <is>
-          <t>Explicitly not the suggested network; cross-links to it.</t>
+          <t>Disabled until the description is read to the end.</t>
         </is>
       </c>
       <c r="K76" s="12" t="inlineStr">
         <is>
-          <t>NH network screen</t>
+          <t>HM H-00 progress</t>
         </is>
       </c>
       <c r="L76" s="12" t="inlineStr">
         <is>
-          <t>A-13</t>
+          <t>A-24</t>
         </is>
       </c>
       <c r="M76" s="12" t="inlineStr">
         <is>
-          <t>NH OI (org chart)</t>
-        </is>
-      </c>
-      <c r="N76" s="15" t="inlineStr">
-        <is>
-          <t>Open — delivery undefined</t>
+          <t>Janine 1:1</t>
+        </is>
+      </c>
+      <c r="N76" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6431,32 @@
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>Confirmation</t>
+          <t>Dissent</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>'I've read my job description and confirm…'</t>
+          <t>'This doesn't match what I agreed' → free text → Under review</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Action + text</t>
         </is>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
         <is>
-          <t>Unchecked</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>Disabled until the description is read to the end.</t>
+          <t>Hides the acknowledgement, changes the primary action, sets task to Under review.</t>
         </is>
       </c>
       <c r="K77" s="10" t="inlineStr">
@@ -6442,12 +6466,12 @@
       </c>
       <c r="L77" s="10" t="inlineStr">
         <is>
-          <t>A-24</t>
+          <t>A-27</t>
         </is>
       </c>
       <c r="M77" s="10" t="inlineStr">
         <is>
-          <t>Janine 1:1</t>
+          <t>PRD S1-US02 edge 4</t>
         </is>
       </c>
       <c r="N77" s="13" t="inlineStr">
@@ -6464,67 +6488,67 @@
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t>P-02</t>
+          <t>P-03</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>Review your job description</t>
+          <t>Introduce yourself</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>#/jd</t>
+          <t>#/intro</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>Dissent</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>'This doesn't match what I agreed' → free text → Under review</t>
+          <t>Free text, 500-character limit with live count</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>Action + text</t>
+          <t>Multi line text</t>
         </is>
       </c>
       <c r="H78" s="12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="I78" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Blank</t>
         </is>
       </c>
       <c r="J78" s="12" t="inlineStr">
         <is>
-          <t>Hides the acknowledgement, changes the primary action, sets task to Under review.</t>
+          <t>Limit invented; needed because the text becomes a team post.</t>
         </is>
       </c>
       <c r="K78" s="12" t="inlineStr">
         <is>
-          <t>HM H-00 progress</t>
+          <t>HM forward task</t>
         </is>
       </c>
       <c r="L78" s="12" t="inlineStr">
         <is>
-          <t>A-27</t>
+          <t>A-15</t>
         </is>
       </c>
       <c r="M78" s="12" t="inlineStr">
         <is>
-          <t>PRD S1-US02 edge 4</t>
-        </is>
-      </c>
-      <c r="N78" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>NH OI-12</t>
+        </is>
+      </c>
+      <c r="N78" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6556,32 +6580,32 @@
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>Free text, 500-character limit with live count</t>
+          <t>Three optional prompt chips, dismissible</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>Multi line text</t>
+          <t>Action ×3</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>Recommended</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
         <is>
-          <t>Blank</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>Limit invented; needed because the text becomes a team post.</t>
+          <t>Append, never overwrite. Address blank-page hesitation.</t>
         </is>
       </c>
       <c r="K79" s="10" t="inlineStr">
         <is>
-          <t>HM forward task</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L79" s="10" t="inlineStr">
@@ -6628,47 +6652,47 @@
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>Three optional prompt chips, dismissible</t>
+          <t>Manager preview panel</t>
         </is>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>Action ×3</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H80" s="12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I80" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="J80" s="12" t="inlineStr">
         <is>
-          <t>Append, never overwrite. Address blank-page hesitation.</t>
+          <t>Shows how it will look when forwarded.</t>
         </is>
       </c>
       <c r="K80" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HM H-16</t>
         </is>
       </c>
       <c r="L80" s="12" t="inlineStr">
         <is>
-          <t>A-15</t>
+          <t>A-14</t>
         </is>
       </c>
       <c r="M80" s="12" t="inlineStr">
         <is>
-          <t>NH OI-12</t>
-        </is>
-      </c>
-      <c r="N80" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>Janine 1:1</t>
+        </is>
+      </c>
+      <c r="N80" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6724,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Manager preview panel</t>
+          <t>Explicit sharing model — manager forwards, never auto-posts</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
@@ -6715,12 +6739,12 @@
       </c>
       <c r="I81" s="10" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>Shows how it will look when forwarded.</t>
+          <t>States the model rather than implying it.</t>
         </is>
       </c>
       <c r="K81" s="10" t="inlineStr">
@@ -6735,12 +6759,12 @@
       </c>
       <c r="M81" s="10" t="inlineStr">
         <is>
-          <t>Janine 1:1</t>
-        </is>
-      </c>
-      <c r="N81" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>NH OI-11</t>
+        </is>
+      </c>
+      <c r="N81" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6767,32 +6791,32 @@
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>Consent</t>
         </is>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>Explicit sharing model — manager forwards, never auto-posts</t>
+          <t>'I'm happy for my manager to share this'</t>
         </is>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="H82" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Yes to share</t>
         </is>
       </c>
       <c r="I82" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Unchecked</t>
         </is>
       </c>
       <c r="J82" s="12" t="inlineStr">
         <is>
-          <t>States the model rather than implying it.</t>
+          <t>Without it the text saves but cannot be forwarded — enforced across the join.</t>
         </is>
       </c>
       <c r="K82" s="12" t="inlineStr">
@@ -6802,17 +6826,17 @@
       </c>
       <c r="L82" s="12" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>L-02</t>
         </is>
       </c>
       <c r="M82" s="12" t="inlineStr">
         <is>
-          <t>NH OI-11</t>
-        </is>
-      </c>
-      <c r="N82" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>Future State Seq 6</t>
+        </is>
+      </c>
+      <c r="N82" s="14" t="inlineStr">
+        <is>
+          <t>Gap closed</t>
         </is>
       </c>
     </row>
@@ -6839,12 +6863,12 @@
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>Consent</t>
+          <t>Photo reuse</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>'I'm happy for my manager to share this'</t>
+          <t>'Use my badge photo with this introduction'</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
@@ -6854,7 +6878,7 @@
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>Yes to share</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
@@ -6864,27 +6888,27 @@
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
-          <t>Without it the text saves but cannot be forwarded — enforced across the join.</t>
+          <t>Only offered once a photo exists.</t>
         </is>
       </c>
       <c r="K83" s="10" t="inlineStr">
         <is>
-          <t>HM H-16</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>L-02</t>
+          <t>A-18</t>
         </is>
       </c>
       <c r="M83" s="10" t="inlineStr">
         <is>
-          <t>Future State Seq 6</t>
-        </is>
-      </c>
-      <c r="N83" s="14" t="inlineStr">
-        <is>
-          <t>Gap closed</t>
+          <t>NH Fields P-03.4</t>
+        </is>
+      </c>
+      <c r="N83" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6920,12 @@
       </c>
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t>P-03</t>
+          <t>P-04</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>Introduce yourself</t>
+          <t>Photo for your badge</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
@@ -6911,47 +6935,47 @@
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>Photo reuse</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
-          <t>'Use my badge photo with this introduction'</t>
+          <t>Drag-and-drop / browse, preview with crop guide</t>
         </is>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Attachment</t>
         </is>
       </c>
       <c r="H84" s="12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="I84" s="12" t="inlineStr">
         <is>
-          <t>Unchecked</t>
+          <t>Blank</t>
         </is>
       </c>
       <c r="J84" s="12" t="inlineStr">
         <is>
-          <t>Only offered once a photo exists.</t>
+          <t>Live preview with a circular badge crop.</t>
         </is>
       </c>
       <c r="K84" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CRE badge system</t>
         </is>
       </c>
       <c r="L84" s="12" t="inlineStr">
         <is>
-          <t>A-18</t>
+          <t>A-17</t>
         </is>
       </c>
       <c r="M84" s="12" t="inlineStr">
         <is>
-          <t>NH Fields P-03.4</t>
+          <t>NH Fields P-04.2</t>
         </is>
       </c>
       <c r="N84" s="13" t="inlineStr">
@@ -6983,37 +7007,37 @@
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>Upload</t>
+          <t>Requirements</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>Drag-and-drop / browse, preview with crop guide</t>
+          <t>JPG/PNG · under 5MB · at least 600×600</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>Attachment</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>Recommended</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
         <is>
-          <t>Blank</t>
+          <t>Placeholder</t>
         </is>
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>Live preview with a circular badge crop.</t>
+          <t>Marked as placeholder — the real spec sits with the workplace team.</t>
         </is>
       </c>
       <c r="K85" s="10" t="inlineStr">
         <is>
-          <t>CRE badge system</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L85" s="10" t="inlineStr">
@@ -7023,12 +7047,12 @@
       </c>
       <c r="M85" s="10" t="inlineStr">
         <is>
-          <t>NH Fields P-04.2</t>
-        </is>
-      </c>
-      <c r="N85" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>NH OI-13</t>
+        </is>
+      </c>
+      <c r="N85" s="15" t="inlineStr">
+        <is>
+          <t>Open — content needed</t>
         </is>
       </c>
     </row>
@@ -7055,12 +7079,12 @@
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>Requirements</t>
+          <t>Guidelines</t>
         </is>
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>JPG/PNG · under 5MB · at least 600×600</t>
+          <t>Four guideline lines</t>
         </is>
       </c>
       <c r="G86" s="12" t="inlineStr">
@@ -7080,7 +7104,7 @@
       </c>
       <c r="J86" s="12" t="inlineStr">
         <is>
-          <t>Marked as placeholder — the real spec sits with the workplace team.</t>
+          <t>Marked as placeholder.</t>
         </is>
       </c>
       <c r="K86" s="12" t="inlineStr">
@@ -7127,32 +7151,32 @@
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>Guidelines</t>
+          <t>Consent</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>Four guideline lines</t>
+          <t>Consent naming badge, directory and Teams profile</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Unchecked</t>
         </is>
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>Marked as placeholder.</t>
+          <t>Names all three surfaces, which is broader than a badge.</t>
         </is>
       </c>
       <c r="K87" s="10" t="inlineStr">
@@ -7162,17 +7186,17 @@
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
-          <t>A-17</t>
+          <t>A-18</t>
         </is>
       </c>
       <c r="M87" s="10" t="inlineStr">
         <is>
-          <t>NH OI-13</t>
+          <t>NH OI-14</t>
         </is>
       </c>
       <c r="N87" s="15" t="inlineStr">
         <is>
-          <t>Open — content needed</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -7199,32 +7223,32 @@
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>Consent</t>
+          <t>Variant</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>Consent naming badge, directory and Teams profile</t>
+          <t>Conversion persona: confirm or replace existing photo</t>
         </is>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Conditional block</t>
         </is>
       </c>
       <c r="H88" s="12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Conditional</t>
         </is>
       </c>
       <c r="I88" s="12" t="inlineStr">
         <is>
-          <t>Unchecked</t>
+          <t>Photo on file</t>
         </is>
       </c>
       <c r="J88" s="12" t="inlineStr">
         <is>
-          <t>Names all three surfaces, which is broader than a badge.</t>
+          <t>Replaces the upload for conversion personas.</t>
         </is>
       </c>
       <c r="K88" s="12" t="inlineStr">
@@ -7234,17 +7258,17 @@
       </c>
       <c r="L88" s="12" t="inlineStr">
         <is>
-          <t>A-18</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M88" s="12" t="inlineStr">
         <is>
-          <t>NH OI-14</t>
-        </is>
-      </c>
-      <c r="N88" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>PRD S2-US08 AC1</t>
+        </is>
+      </c>
+      <c r="N88" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -7271,47 +7295,47 @@
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>Variant</t>
+          <t>Timing</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>Conversion persona: confirm or replace existing photo</t>
+          <t>Due earlier than the introduction (badge print lead)</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>Conditional block</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>Conditional</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
         <is>
-          <t>Photo on file</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J89" s="10" t="inlineStr">
         <is>
-          <t>Replaces the upload for conversion personas.</t>
+          <t>Two due dates on one card, explained.</t>
         </is>
       </c>
       <c r="K89" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HM H-00 third-party</t>
         </is>
       </c>
       <c r="L89" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A-16</t>
         </is>
       </c>
       <c r="M89" s="10" t="inlineStr">
         <is>
-          <t>PRD S2-US08 AC1</t>
+          <t>Merge Analysis 4</t>
         </is>
       </c>
       <c r="N89" s="13" t="inlineStr">
@@ -7328,27 +7352,27 @@
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t>P-04</t>
+          <t>P-05</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>Photo for your badge</t>
+          <t>Policies and privacy notices</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>#/intro</t>
+          <t>#/policies</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>Timing</t>
+          <t>Progress</t>
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>Due earlier than the introduction (badge print lead)</t>
+          <t>'N of 6 acknowledged'</t>
         </is>
       </c>
       <c r="G90" s="12" t="inlineStr">
@@ -7363,27 +7387,27 @@
       </c>
       <c r="I90" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Computed</t>
         </is>
       </c>
       <c r="J90" s="12" t="inlineStr">
         <is>
-          <t>Two due dates on one card, explained.</t>
+          <t>Per-document tracking.</t>
         </is>
       </c>
       <c r="K90" s="12" t="inlineStr">
         <is>
-          <t>HM H-00 third-party</t>
+          <t>HM H-00 (status only)</t>
         </is>
       </c>
       <c r="L90" s="12" t="inlineStr">
         <is>
-          <t>A-16</t>
+          <t>M-03 / L-05</t>
         </is>
       </c>
       <c r="M90" s="12" t="inlineStr">
         <is>
-          <t>Merge Analysis 4</t>
+          <t>PRD S2-US19 AC1</t>
         </is>
       </c>
       <c r="N90" s="13" t="inlineStr">
@@ -7415,47 +7439,47 @@
       </c>
       <c r="E91" s="10" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>'N of 6 acknowledged'</t>
+          <t>Acceptable Use Policy</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Doc + ack</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
         <is>
-          <t>Computed</t>
+          <t>Content object</t>
         </is>
       </c>
       <c r="J91" s="10" t="inlineStr">
         <is>
-          <t>Per-document tracking.</t>
+          <t>Scroll-gated acknowledgement. Hosts the country addendum.</t>
         </is>
       </c>
       <c r="K91" s="10" t="inlineStr">
         <is>
-          <t>HM H-00 (status only)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L91" s="10" t="inlineStr">
         <is>
-          <t>M-03 / L-05</t>
+          <t>A-24</t>
         </is>
       </c>
       <c r="M91" s="10" t="inlineStr">
         <is>
-          <t>PRD S2-US19 AC1</t>
+          <t>Design Logic row 1</t>
         </is>
       </c>
       <c r="N91" s="13" t="inlineStr">
@@ -7492,7 +7516,7 @@
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
-          <t>Acceptable Use Policy</t>
+          <t>Code of Business Conduct — external site</t>
         </is>
       </c>
       <c r="G92" s="12" t="inlineStr">
@@ -7507,12 +7531,12 @@
       </c>
       <c r="I92" s="12" t="inlineStr">
         <is>
-          <t>Content object</t>
+          <t>External</t>
         </is>
       </c>
       <c r="J92" s="12" t="inlineStr">
         <is>
-          <t>Scroll-gated acknowledgement. Hosts the country addendum.</t>
+          <t>Opens in a new tab, needs Equinix sign-in, return state remembers position.</t>
         </is>
       </c>
       <c r="K92" s="12" t="inlineStr">
@@ -7527,12 +7551,12 @@
       </c>
       <c r="M92" s="12" t="inlineStr">
         <is>
-          <t>Design Logic row 1</t>
-        </is>
-      </c>
-      <c r="N92" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>Design Logic row 2</t>
+        </is>
+      </c>
+      <c r="N92" s="15" t="inlineStr">
+        <is>
+          <t>Open — see Alignment G-04</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7588,7 @@
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>Code of Business Conduct — external site</t>
+          <t>Whistleblower Protection Policy</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
@@ -7579,12 +7603,12 @@
       </c>
       <c r="I93" s="10" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>Content object</t>
         </is>
       </c>
       <c r="J93" s="10" t="inlineStr">
         <is>
-          <t>Opens in a new tab, needs Equinix sign-in, return state remembers position.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K93" s="10" t="inlineStr">
@@ -7599,12 +7623,12 @@
       </c>
       <c r="M93" s="10" t="inlineStr">
         <is>
-          <t>Design Logic row 2</t>
-        </is>
-      </c>
-      <c r="N93" s="15" t="inlineStr">
-        <is>
-          <t>Open — see Alignment G-04</t>
+          <t>Design Logic row 4</t>
+        </is>
+      </c>
+      <c r="N93" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7660,7 @@
       </c>
       <c r="F94" s="12" t="inlineStr">
         <is>
-          <t>Whistleblower Protection Policy</t>
+          <t>Securities Trading Policy</t>
         </is>
       </c>
       <c r="G94" s="12" t="inlineStr">
@@ -7646,7 +7670,7 @@
       </c>
       <c r="H94" s="12" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Required (assumed)</t>
         </is>
       </c>
       <c r="I94" s="12" t="inlineStr">
@@ -7656,7 +7680,7 @@
       </c>
       <c r="J94" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Acknowledgement requirement is blank in the source.</t>
         </is>
       </c>
       <c r="K94" s="12" t="inlineStr">
@@ -7666,17 +7690,17 @@
       </c>
       <c r="L94" s="12" t="inlineStr">
         <is>
-          <t>A-24</t>
+          <t>A-19</t>
         </is>
       </c>
       <c r="M94" s="12" t="inlineStr">
         <is>
-          <t>Design Logic row 4</t>
-        </is>
-      </c>
-      <c r="N94" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>NH OI-06</t>
+        </is>
+      </c>
+      <c r="N94" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -7708,7 +7732,7 @@
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>Securities Trading Policy</t>
+          <t>Employee Data Privacy Notice</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
@@ -7718,7 +7742,7 @@
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>Required (assumed)</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr">
@@ -7728,7 +7752,7 @@
       </c>
       <c r="J95" s="10" t="inlineStr">
         <is>
-          <t>Acknowledgement requirement is blank in the source.</t>
+          <t>Global notice + conditional country addendum.</t>
         </is>
       </c>
       <c r="K95" s="10" t="inlineStr">
@@ -7738,17 +7762,17 @@
       </c>
       <c r="L95" s="10" t="inlineStr">
         <is>
-          <t>A-19</t>
+          <t>A-24</t>
         </is>
       </c>
       <c r="M95" s="10" t="inlineStr">
         <is>
-          <t>NH OI-06</t>
+          <t>PRD v1.4 DPN</t>
         </is>
       </c>
       <c r="N95" s="15" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Open — see Alignment G-02</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7804,7 @@
       </c>
       <c r="F96" s="12" t="inlineStr">
         <is>
-          <t>Employee Data Privacy Notice</t>
+          <t>Self-Identification Privacy Notice</t>
         </is>
       </c>
       <c r="G96" s="12" t="inlineStr">
@@ -7800,27 +7824,27 @@
       </c>
       <c r="J96" s="12" t="inlineStr">
         <is>
-          <t>Global notice + conditional country addendum.</t>
+          <t>Must be paired with the self-ID block on P-01.</t>
         </is>
       </c>
       <c r="K96" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P-01c self-ID</t>
         </is>
       </c>
       <c r="L96" s="12" t="inlineStr">
         <is>
-          <t>A-24</t>
+          <t>A-07</t>
         </is>
       </c>
       <c r="M96" s="12" t="inlineStr">
         <is>
-          <t>PRD v1.4 DPN</t>
-        </is>
-      </c>
-      <c r="N96" s="15" t="inlineStr">
-        <is>
-          <t>Open — see Alignment G-02</t>
+          <t>Design Logic row 11</t>
+        </is>
+      </c>
+      <c r="N96" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -7847,47 +7871,47 @@
       </c>
       <c r="E97" s="10" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Country variant</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>Self-Identification Privacy Notice</t>
+          <t>Japan addendum nested inside the AUP</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
         <is>
-          <t>Doc + ack</t>
+          <t>Conditional section</t>
         </is>
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Conditional</t>
         </is>
       </c>
       <c r="I97" s="10" t="inlineStr">
         <is>
-          <t>Content object</t>
+          <t>Country of hire</t>
         </is>
       </c>
       <c r="J97" s="10" t="inlineStr">
         <is>
-          <t>Must be paired with the self-ID block on P-01.</t>
+          <t>One global policy with a local section — not a separate document.</t>
         </is>
       </c>
       <c r="K97" s="10" t="inlineStr">
         <is>
-          <t>P-01c self-ID</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L97" s="10" t="inlineStr">
         <is>
-          <t>A-07</t>
+          <t>A-20</t>
         </is>
       </c>
       <c r="M97" s="10" t="inlineStr">
         <is>
-          <t>Design Logic row 11</t>
+          <t>Design Logic row 1</t>
         </is>
       </c>
       <c r="N97" s="13" t="inlineStr">
@@ -7919,32 +7943,32 @@
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>Country variant</t>
+          <t>Metadata</t>
         </is>
       </c>
       <c r="F98" s="12" t="inlineStr">
         <is>
-          <t>Japan addendum nested inside the AUP</t>
+          <t>Version and language recorded on acknowledgement</t>
         </is>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
-          <t>Conditional section</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H98" s="12" t="inlineStr">
         <is>
-          <t>Conditional</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I98" s="12" t="inlineStr">
         <is>
-          <t>Country of hire</t>
+          <t>System</t>
         </is>
       </c>
       <c r="J98" s="12" t="inlineStr">
         <is>
-          <t>One global policy with a local section — not a separate document.</t>
+          <t>Quiet confirmation that it was recorded.</t>
         </is>
       </c>
       <c r="K98" s="12" t="inlineStr">
@@ -7954,12 +7978,12 @@
       </c>
       <c r="L98" s="12" t="inlineStr">
         <is>
-          <t>A-20</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M98" s="12" t="inlineStr">
         <is>
-          <t>Design Logic row 1</t>
+          <t>PRD 3.5</t>
         </is>
       </c>
       <c r="N98" s="13" t="inlineStr">
@@ -7991,32 +8015,32 @@
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>Metadata</t>
+          <t>Reading material</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>Version and language recorded on acknowledgement</t>
+          <t>Company factsheet · Employee handbook (country)</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Reference ×2</t>
         </is>
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I99" s="10" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Content hub</t>
         </is>
       </c>
       <c r="J99" s="10" t="inlineStr">
         <is>
-          <t>Quiet confirmation that it was recorded.</t>
+          <t>Grouped separately so they do not read as outstanding tasks.</t>
         </is>
       </c>
       <c r="K99" s="10" t="inlineStr">
@@ -8031,12 +8055,12 @@
       </c>
       <c r="M99" s="10" t="inlineStr">
         <is>
-          <t>PRD 3.5</t>
-        </is>
-      </c>
-      <c r="N99" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>Design Logic rows 3, 8</t>
+        </is>
+      </c>
+      <c r="N99" s="15" t="inlineStr">
+        <is>
+          <t>Open — see Alignment G-03</t>
         </is>
       </c>
     </row>
@@ -8063,32 +8087,32 @@
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
-          <t>Reading material</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="F100" s="12" t="inlineStr">
         <is>
-          <t>Company factsheet · Employee handbook (country)</t>
+          <t>Single submit for the whole pack</t>
         </is>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
-          <t>Reference ×2</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="H100" s="12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I100" s="12" t="inlineStr">
         <is>
-          <t>Content hub</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J100" s="12" t="inlineStr">
         <is>
-          <t>Grouped separately so they do not read as outstanding tasks.</t>
+          <t>Disabled until every required acknowledgement is ticked. Partial state persists.</t>
         </is>
       </c>
       <c r="K100" s="12" t="inlineStr">
@@ -8103,12 +8127,12 @@
       </c>
       <c r="M100" s="12" t="inlineStr">
         <is>
-          <t>Design Logic rows 3, 8</t>
-        </is>
-      </c>
-      <c r="N100" s="15" t="inlineStr">
-        <is>
-          <t>Open — see Alignment G-03</t>
+          <t>PRD S2-US19 AC2</t>
+        </is>
+      </c>
+      <c r="N100" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -8120,67 +8144,67 @@
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>P-05</t>
+          <t>NH-NET</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Policies and privacy notices</t>
+          <t>Your suggested network</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>#/policies</t>
+          <t>#/network</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Waiting state</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>Single submit for the whole pack</t>
+          <t>'Priya hasn't named anyone yet'</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I101" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HM network task</t>
         </is>
       </c>
       <c r="J101" s="10" t="inlineStr">
         <is>
-          <t>Disabled until every required acknowledgement is ticked. Partial state persists.</t>
+          <t>The whole screen is empty until the manager acts — the dependency is visible.</t>
         </is>
       </c>
       <c r="K101" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HM H-11</t>
         </is>
       </c>
       <c r="L101" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>L-06</t>
         </is>
       </c>
       <c r="M101" s="10" t="inlineStr">
         <is>
-          <t>PRD S2-US19 AC2</t>
-        </is>
-      </c>
-      <c r="N101" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>HM H-11</t>
+        </is>
+      </c>
+      <c r="N101" s="14" t="inlineStr">
+        <is>
+          <t>Gap closed</t>
         </is>
       </c>
     </row>
@@ -8207,12 +8231,12 @@
       </c>
       <c r="E102" s="12" t="inlineStr">
         <is>
-          <t>Waiting state</t>
+          <t>People</t>
         </is>
       </c>
       <c r="F102" s="12" t="inlineStr">
         <is>
-          <t>'Priya hasn't named anyone yet'</t>
+          <t>Person card: name, role, department</t>
         </is>
       </c>
       <c r="G102" s="12" t="inlineStr">
@@ -8227,12 +8251,12 @@
       </c>
       <c r="I102" s="12" t="inlineStr">
         <is>
-          <t>HM network task</t>
+          <t>HM selection</t>
         </is>
       </c>
       <c r="J102" s="12" t="inlineStr">
         <is>
-          <t>The whole screen is empty until the manager acts — the dependency is visible.</t>
+          <t>Rendered from the manager's picks.</t>
         </is>
       </c>
       <c r="K102" s="12" t="inlineStr">
@@ -8284,7 +8308,7 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>Person card: name, role, department</t>
+          <t>'Why Priya picked them' — verbatim</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
@@ -8299,12 +8323,12 @@
       </c>
       <c r="I103" s="10" t="inlineStr">
         <is>
-          <t>HM selection</t>
+          <t>HM free text</t>
         </is>
       </c>
       <c r="J103" s="10" t="inlineStr">
         <is>
-          <t>Rendered from the manager's picks.</t>
+          <t>The manager's reason shown to the new hire exactly as written.</t>
         </is>
       </c>
       <c r="K103" s="10" t="inlineStr">
@@ -8319,12 +8343,12 @@
       </c>
       <c r="M103" s="10" t="inlineStr">
         <is>
-          <t>HM H-11</t>
-        </is>
-      </c>
-      <c r="N103" s="14" t="inlineStr">
-        <is>
-          <t>Gap closed</t>
+          <t>1:1 with platform owner</t>
+        </is>
+      </c>
+      <c r="N103" s="15" t="inlineStr">
+        <is>
+          <t>Open — see Alignment G-12</t>
         </is>
       </c>
     </row>
@@ -8351,52 +8375,52 @@
       </c>
       <c r="E104" s="12" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Booking</t>
         </is>
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
-          <t>'Why Priya picked them' — verbatim</t>
+          <t>Three suggested 1:1 slots per person</t>
         </is>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Action ×3</t>
         </is>
       </c>
       <c r="H104" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I104" s="12" t="inlineStr">
         <is>
-          <t>HM free text</t>
+          <t>Derived from start date</t>
         </is>
       </c>
       <c r="J104" s="12" t="inlineStr">
         <is>
-          <t>The manager's reason shown to the new hire exactly as written.</t>
+          <t>Booking is optional and per-person.</t>
         </is>
       </c>
       <c r="K104" s="12" t="inlineStr">
         <is>
-          <t>HM H-11</t>
+          <t>Outlook</t>
         </is>
       </c>
       <c r="L104" s="12" t="inlineStr">
         <is>
-          <t>L-06</t>
+          <t>A-43</t>
         </is>
       </c>
       <c r="M104" s="12" t="inlineStr">
         <is>
-          <t>1:1 with platform owner</t>
+          <t>Lucid manager lane</t>
         </is>
       </c>
       <c r="N104" s="15" t="inlineStr">
         <is>
-          <t>Open — see Alignment G-12</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8423,37 +8447,37 @@
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>Booking</t>
+          <t>Framing</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>Three suggested 1:1 slots per person</t>
+          <t>Network vs buddy vs team — three-way distinction</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>Action ×3</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I105" s="10" t="inlineStr">
         <is>
-          <t>Derived from start date</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J105" s="10" t="inlineStr">
         <is>
-          <t>Booking is optional and per-person.</t>
+          <t>Explicitly not the org chart; explicitly not the buddy.</t>
         </is>
       </c>
       <c r="K105" s="10" t="inlineStr">
         <is>
-          <t>Outlook</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L105" s="10" t="inlineStr">
@@ -8463,12 +8487,12 @@
       </c>
       <c r="M105" s="10" t="inlineStr">
         <is>
-          <t>Lucid manager lane</t>
-        </is>
-      </c>
-      <c r="N105" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>HM spec §4</t>
+        </is>
+      </c>
+      <c r="N105" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -8480,47 +8504,47 @@
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t>NH-NET</t>
+          <t>P-00</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>Your suggested network</t>
+          <t>Portal landing / task list</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>#/network</t>
+          <t>#/</t>
         </is>
       </c>
       <c r="E106" s="12" t="inlineStr">
         <is>
-          <t>Framing</t>
+          <t>Inside Equinix</t>
         </is>
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>Network vs buddy vs team — three-way distinction</t>
+          <t>Carousel — six chapters, rotating, with manual navigation</t>
         </is>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="H106" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I106" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Content hub</t>
         </is>
       </c>
       <c r="J106" s="12" t="inlineStr">
         <is>
-          <t>Explicitly not the org chart; explicitly not the buddy.</t>
+          <t>Sits above the progress tracker. Nothing tracked, nothing required. Rail link kept alongside it.</t>
         </is>
       </c>
       <c r="K106" s="12" t="inlineStr">
@@ -8530,17 +8554,17 @@
       </c>
       <c r="L106" s="12" t="inlineStr">
         <is>
-          <t>A-43</t>
+          <t>A-35</t>
         </is>
       </c>
       <c r="M106" s="12" t="inlineStr">
         <is>
-          <t>HM spec §4</t>
-        </is>
-      </c>
-      <c r="N106" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>PRD v1.4 UI request</t>
+        </is>
+      </c>
+      <c r="N106" s="14" t="inlineStr">
+        <is>
+          <t>Gap closed</t>
         </is>
       </c>
     </row>
@@ -8552,32 +8576,32 @@
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>NH-FLOW</t>
+          <t>NH-SD</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Flow overview (review screen)</t>
+          <t>Confirm your start date</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>#/flow</t>
+          <t>#/startdate</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>Diagram</t>
+          <t>Confirmation</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>Whole pre-Day 1 sequence against the timeline</t>
+          <t>Your start date, from your offer</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
         <is>
-          <t>Diagram</t>
+          <t>Read-only</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
@@ -8587,280 +8611,280 @@
       </c>
       <c r="I107" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="J107" s="10" t="inlineStr">
         <is>
-          <t>Three lanes: yours, opens later, other teams. Notes the post-Day 1 overflow.</t>
+          <t>Every other due date in the portal is an offset from this.</t>
         </is>
       </c>
       <c r="K107" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HM readiness + calendar</t>
         </is>
       </c>
       <c r="L107" s="10" t="inlineStr">
         <is>
-          <t>A-48</t>
+          <t>A-49</t>
         </is>
       </c>
       <c r="M107" s="10" t="inlineStr">
         <is>
-          <t>NH Stage 6</t>
-        </is>
-      </c>
-      <c r="N107" s="11" t="inlineStr">
-        <is>
-          <t>Mockup only</t>
+          <t>Future State Seq 4</t>
+        </is>
+      </c>
+      <c r="N107" s="14" t="inlineStr">
+        <is>
+          <t>Gap closed</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
         <is>
-          <t>Hiring manager</t>
+          <t>New hire</t>
         </is>
       </c>
       <c r="B108" s="12" t="inlineStr">
         <is>
-          <t>H-00</t>
+          <t>NH-SD</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>New hire readiness view</t>
+          <t>Confirm your start date</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>#/hm/</t>
+          <t>#/startdate</t>
         </is>
       </c>
       <c r="E108" s="12" t="inlineStr">
         <is>
-          <t>Selector</t>
+          <t>Confirmation</t>
         </is>
       </c>
       <c r="F108" s="12" t="inlineStr">
         <is>
-          <t>New hire selector (multiple concurrent hires)</t>
+          <t>Yes, that's right</t>
         </is>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
-          <t>Reference widget</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="H108" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I108" s="12" t="inlineStr">
         <is>
-          <t>Hires reporting to this manager</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J108" s="12" t="inlineStr">
         <is>
-          <t>Second hire shown read-only to prove the multi-hire view.</t>
+          <t>Completes the task and anchors the schedule.</t>
         </is>
       </c>
       <c r="K108" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HM readiness</t>
         </is>
       </c>
       <c r="L108" s="12" t="inlineStr">
         <is>
-          <t>M-13</t>
+          <t>A-49</t>
         </is>
       </c>
       <c r="M108" s="12" t="inlineStr">
         <is>
-          <t>HM Fields H-00.1</t>
-        </is>
-      </c>
-      <c r="N108" s="15" t="inlineStr">
-        <is>
-          <t>Open — volume unknown</t>
+          <t>Future State Seq 4</t>
+        </is>
+      </c>
+      <c r="N108" s="14" t="inlineStr">
+        <is>
+          <t>Gap closed</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>Hiring manager</t>
+          <t>New hire</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>H-00</t>
+          <t>NH-SD</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>New hire readiness view</t>
+          <t>Confirm your start date</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>#/hm/</t>
+          <t>#/startdate</t>
         </is>
       </c>
       <c r="E109" s="10" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Change</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>Readiness score</t>
+          <t>I need a different date → date + reason → request</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Action + fields</t>
         </is>
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I109" s="10" t="inlineStr">
         <is>
-          <t>Computed</t>
+          <t>Blank</t>
         </is>
       </c>
       <c r="J109" s="10" t="inlineStr">
         <is>
-          <t>Plain count of tasks done over tasks assigned, with the absence of a formula stated on screen.</t>
+          <t>Puts the task into a requested state. Dates stay put until agreed.</t>
         </is>
       </c>
       <c r="K109" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HM readiness</t>
         </is>
       </c>
       <c r="L109" s="10" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>L-11</t>
         </is>
       </c>
       <c r="M109" s="10" t="inlineStr">
         <is>
-          <t>HM OI-02</t>
+          <t>Future State Seq 4</t>
         </is>
       </c>
       <c r="N109" s="15" t="inlineStr">
         <is>
-          <t>Open — BLOCKS BUILD</t>
+          <t>Open — resolution undefined</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
         <is>
-          <t>Hiring manager</t>
+          <t>New hire</t>
         </is>
       </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t>H-00</t>
+          <t>NH-BG</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>New hire readiness view</t>
+          <t>Start your background check</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>#/hm/</t>
+          <t>#/bgcheck</t>
         </is>
       </c>
       <c r="E110" s="12" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Launch</t>
         </is>
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>Breakdown by owner: new hire / you / other teams</t>
+          <t>Start the check (opens the screening provider)</t>
         </is>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
-          <t>Display ×3</t>
+          <t>External action</t>
         </is>
       </c>
       <c r="H110" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I110" s="12" t="inlineStr">
         <is>
-          <t>Computed</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J110" s="12" t="inlineStr">
         <is>
-          <t>Separates what the manager controls from what they do not.</t>
+          <t>The new hire launches it; it runs externally and reports status back.</t>
         </is>
       </c>
       <c r="K110" s="12" t="inlineStr">
         <is>
-          <t>NH progress</t>
+          <t>HM third-party</t>
         </is>
       </c>
       <c r="L110" s="12" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>A-50</t>
         </is>
       </c>
       <c r="M110" s="12" t="inlineStr">
         <is>
-          <t>PRD 3.6</t>
-        </is>
-      </c>
-      <c r="N110" s="11" t="inlineStr">
-        <is>
-          <t>Mockup only</t>
+          <t>Future State Seq 3</t>
+        </is>
+      </c>
+      <c r="N110" s="14" t="inlineStr">
+        <is>
+          <t>Gap closed</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>Hiring manager</t>
+          <t>New hire</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>H-00</t>
+          <t>NH-BG</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>New hire readiness view</t>
+          <t>Start your background check</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>#/hm/</t>
+          <t>#/bgcheck</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>New hire name, start date, days remaining</t>
+          <t>Running — nothing further from you</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
@@ -8875,156 +8899,156 @@
       </c>
       <c r="I111" s="10" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Provider</t>
         </is>
       </c>
       <c r="J111" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Manager sees it running, never its contents.</t>
         </is>
       </c>
       <c r="K111" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HM progress row</t>
         </is>
       </c>
       <c r="L111" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A-50 / L-05</t>
         </is>
       </c>
       <c r="M111" s="10" t="inlineStr">
         <is>
-          <t>HM Fields H-00.3</t>
-        </is>
-      </c>
-      <c r="N111" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>Future State Seq 3</t>
+        </is>
+      </c>
+      <c r="N111" s="14" t="inlineStr">
+        <is>
+          <t>Gap closed</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
         <is>
-          <t>Hiring manager</t>
+          <t>New hire</t>
         </is>
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t>H-00</t>
+          <t>P-00</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>New hire readiness view</t>
+          <t>Portal landing / task list</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>#/hm/</t>
+          <t>#/</t>
         </is>
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
-          <t>Blockers</t>
+          <t>Coming up</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>Blockers and escalation panel</t>
+          <t>Equinix Corporate Card Request — Day 2</t>
         </is>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>Display + action</t>
+          <t>Disabled card</t>
         </is>
       </c>
       <c r="H112" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Conditional</t>
         </is>
       </c>
       <c r="I112" s="12" t="inlineStr">
         <is>
-          <t>Late/blocked tasks</t>
+          <t>HM card answer</t>
         </is>
       </c>
       <c r="J112" s="12" t="inlineStr">
         <is>
-          <t>Computed live: unordered computer, unassigned buddy near Day −3, overdue new hire tasks, blocked stack.</t>
+          <t>Appears only when the manager answers yes. A no creates nothing at all.</t>
         </is>
       </c>
       <c r="K112" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HM H-06</t>
         </is>
       </c>
       <c r="L112" s="12" t="inlineStr">
         <is>
-          <t>M-16</t>
+          <t>L-10</t>
         </is>
       </c>
       <c r="M112" s="12" t="inlineStr">
         <is>
-          <t>HM Fields H-00.8</t>
-        </is>
-      </c>
-      <c r="N112" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>PRD v1.4</t>
+        </is>
+      </c>
+      <c r="N112" s="14" t="inlineStr">
+        <is>
+          <t>Gap closed</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>Hiring manager</t>
+          <t>New hire</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>H-00</t>
+          <t>P-05</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>New hire readiness view</t>
+          <t>Policies and privacy notices</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>#/hm/</t>
+          <t>#/policies</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
         <is>
-          <t>Your tasks</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>Task cards with disposition badges</t>
+          <t>Served in the language required for the country of hire</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
         <is>
-          <t>Task cards ×7-8</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I113" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Country of hire</t>
         </is>
       </c>
       <c r="J113" s="10" t="inlineStr">
         <is>
-          <t>Every card carries keep / exception-only / automate / remove / adds work.</t>
+          <t>Derived, not chosen. Switching country switches the served language.</t>
         </is>
       </c>
       <c r="K113" s="10" t="inlineStr">
@@ -9034,69 +9058,69 @@
       </c>
       <c r="L113" s="10" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="M113" s="10" t="inlineStr">
         <is>
-          <t>HM Task Disposition</t>
-        </is>
-      </c>
-      <c r="N113" s="11" t="inlineStr">
-        <is>
-          <t>Mockup device</t>
+          <t>PRD v1.4 DPN</t>
+        </is>
+      </c>
+      <c r="N113" s="14" t="inlineStr">
+        <is>
+          <t>Gap closed</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
         <is>
-          <t>Hiring manager</t>
+          <t>New hire</t>
         </is>
       </c>
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t>H-00</t>
+          <t>P-05</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>New hire readiness view</t>
+          <t>Policies and privacy notices</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>#/hm/</t>
+          <t>#/policies</t>
         </is>
       </c>
       <c r="E114" s="12" t="inlineStr">
         <is>
-          <t>Your tasks</t>
+          <t>Reference pack</t>
         </is>
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>Link to the subtraction review</t>
+          <t>Country handbook bundle with its real size</t>
         </is>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>Link</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H114" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I114" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Current-state process</t>
         </is>
       </c>
       <c r="J114" s="12" t="inlineStr">
         <is>
-          <t>The argument screen for this side.</t>
+          <t>US: handbook + 25 state addenda + benefits booklet + GovDocs = 28 documents.</t>
         </is>
       </c>
       <c r="K114" s="12" t="inlineStr">
@@ -9106,54 +9130,54 @@
       </c>
       <c r="L114" s="12" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>A-51</t>
         </is>
       </c>
       <c r="M114" s="12" t="inlineStr">
         <is>
-          <t>HM Task Disposition</t>
-        </is>
-      </c>
-      <c r="N114" s="11" t="inlineStr">
-        <is>
-          <t>Mockup device</t>
+          <t>CR PC current state</t>
+        </is>
+      </c>
+      <c r="N114" s="14" t="inlineStr">
+        <is>
+          <t>Gap closed</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>Hiring manager</t>
+          <t>New hire</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>H-00</t>
+          <t>P-05</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>New hire readiness view</t>
+          <t>Policies and privacy notices</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>#/hm/</t>
+          <t>#/policies</t>
         </is>
       </c>
       <c r="E115" s="10" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>Reference pack</t>
         </is>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>Equipment orders table (identical to the new hire's)</t>
+          <t>Flag: shown because it is true today, not because it is right</t>
         </is>
       </c>
       <c r="G115" s="10" t="inlineStr">
         <is>
-          <t>Display table</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H115" s="10" t="inlineStr">
@@ -9163,141 +9187,141 @@
       </c>
       <c r="I115" s="10" t="inlineStr">
         <is>
-          <t>Equipment Orders</t>
+          <t>Current-state process</t>
         </is>
       </c>
       <c r="J115" s="10" t="inlineStr">
         <is>
-          <t>One source, both sides. Names who each item waits on.</t>
+          <t>Names the 24 addenda that do not apply, and the 416 instances across the whole process.</t>
         </is>
       </c>
       <c r="K115" s="10" t="inlineStr">
         <is>
-          <t>NH equipment</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L115" s="10" t="inlineStr">
         <is>
-          <t>M-16 / L-04</t>
+          <t>A-51</t>
         </is>
       </c>
       <c r="M115" s="10" t="inlineStr">
         <is>
-          <t>Live UAT portal</t>
-        </is>
-      </c>
-      <c r="N115" s="14" t="inlineStr">
-        <is>
-          <t>Gap closed</t>
+          <t>CR PC current state</t>
+        </is>
+      </c>
+      <c r="N115" s="15" t="inlineStr">
+        <is>
+          <t>Open — decision needed</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
         <is>
-          <t>Hiring manager</t>
+          <t>New hire</t>
         </is>
       </c>
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t>H-00</t>
+          <t>P-01c</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>New hire readiness view</t>
+          <t>Personal details — Tab 3 Preferences</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>#/hm/</t>
+          <t>#/details</t>
         </is>
       </c>
       <c r="E116" s="12" t="inlineStr">
         <is>
-          <t>New hire progress</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>Task names + status, content withheld</t>
+          <t>Language for messages from us (communications only)</t>
         </is>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
-          <t>Display ×5</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="H116" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I116" s="12" t="inlineStr">
         <is>
-          <t>New hire task records</t>
+          <t>Country of hire</t>
         </is>
       </c>
       <c r="J116" s="12" t="inlineStr">
         <is>
-          <t>Sensitive rows marked 'Detail hidden' with what is withheld named.</t>
+          <t>Demoted. States that document language is set by law, not preference.</t>
         </is>
       </c>
       <c r="K116" s="12" t="inlineStr">
         <is>
-          <t>NH all tasks</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L116" s="12" t="inlineStr">
         <is>
-          <t>M-03 / L-05</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="M116" s="12" t="inlineStr">
         <is>
-          <t>HM OI-03</t>
-        </is>
-      </c>
-      <c r="N116" s="15" t="inlineStr">
-        <is>
-          <t>Open — BLOCKS BUILD</t>
+          <t>PRD v1.4 DPN</t>
+        </is>
+      </c>
+      <c r="N116" s="14" t="inlineStr">
+        <is>
+          <t>Gap closed</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>Hiring manager</t>
+          <t>New hire</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>H-00</t>
+          <t>NH-FLOW</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>New hire readiness view</t>
+          <t>Flow overview (review screen)</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>#/hm/</t>
+          <t>#/flow</t>
         </is>
       </c>
       <c r="E117" s="10" t="inlineStr">
         <is>
-          <t>Third party</t>
+          <t>Diagram</t>
         </is>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t>PEX / EUT / CRE task status</t>
+          <t>Whole pre-Day 1 sequence against the timeline</t>
         </is>
       </c>
       <c r="G117" s="10" t="inlineStr">
         <is>
-          <t>Display ×3</t>
+          <t>Diagram</t>
         </is>
       </c>
       <c r="H117" s="10" t="inlineStr">
@@ -9307,32 +9331,32 @@
       </c>
       <c r="I117" s="10" t="inlineStr">
         <is>
-          <t>Task records across teams</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J117" s="10" t="inlineStr">
         <is>
-          <t>Badge print reflects whether the new hire submitted a photo.</t>
+          <t>Three lanes: yours, opens later, other teams. Notes the post-Day 1 overflow.</t>
         </is>
       </c>
       <c r="K117" s="10" t="inlineStr">
         <is>
-          <t>NH photo task</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L117" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A-48</t>
         </is>
       </c>
       <c r="M117" s="10" t="inlineStr">
         <is>
-          <t>PRD S2-US13 AC1</t>
-        </is>
-      </c>
-      <c r="N117" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>NH Stage 6</t>
+        </is>
+      </c>
+      <c r="N117" s="11" t="inlineStr">
+        <is>
+          <t>Mockup only</t>
         </is>
       </c>
     </row>
@@ -9359,32 +9383,32 @@
       </c>
       <c r="E118" s="12" t="inlineStr">
         <is>
-          <t>Rail</t>
+          <t>Selector</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
-          <t>New hire contact card</t>
+          <t>New hire selector (multiple concurrent hires)</t>
         </is>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>Contact card</t>
+          <t>Reference widget</t>
         </is>
       </c>
       <c r="H118" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I118" s="12" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Hires reporting to this manager</t>
         </is>
       </c>
       <c r="J118" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Second hire shown read-only to prove the multi-hire view.</t>
         </is>
       </c>
       <c r="K118" s="12" t="inlineStr">
@@ -9394,17 +9418,17 @@
       </c>
       <c r="L118" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M-13</t>
         </is>
       </c>
       <c r="M118" s="12" t="inlineStr">
         <is>
-          <t>HM spec</t>
-        </is>
-      </c>
-      <c r="N118" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>HM Fields H-00.1</t>
+        </is>
+      </c>
+      <c r="N118" s="15" t="inlineStr">
+        <is>
+          <t>Open — volume unknown</t>
         </is>
       </c>
     </row>
@@ -9431,12 +9455,12 @@
       </c>
       <c r="E119" s="10" t="inlineStr">
         <is>
-          <t>Rail</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>Notice: the new hire already has your details</t>
+          <t>Readiness score</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
@@ -9451,32 +9475,32 @@
       </c>
       <c r="I119" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Computed</t>
         </is>
       </c>
       <c r="J119" s="10" t="inlineStr">
         <is>
-          <t>Tells the manager they are contactable pre-Day 1, and that nothing sets a response expectation.</t>
+          <t>Plain count of tasks done over tasks assigned, with the absence of a formula stated on screen.</t>
         </is>
       </c>
       <c r="K119" s="10" t="inlineStr">
         <is>
-          <t>NH rail</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L119" s="10" t="inlineStr">
         <is>
-          <t>L-03</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="M119" s="10" t="inlineStr">
         <is>
-          <t>HM OI-23</t>
+          <t>HM OI-02</t>
         </is>
       </c>
       <c r="N119" s="15" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Open — BLOCKS BUILD</t>
         </is>
       </c>
     </row>
@@ -9503,52 +9527,52 @@
       </c>
       <c r="E120" s="12" t="inlineStr">
         <is>
-          <t>Rail</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>Quick confirm: your contact details</t>
+          <t>Breakdown by owner: new hire / you / other teams</t>
         </is>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Display ×3</t>
         </is>
       </c>
       <c r="H120" s="12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I120" s="12" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Computed</t>
         </is>
       </c>
       <c r="J120" s="12" t="inlineStr">
         <is>
-          <t>One tap. Was a separate task; folded in because it needs no judgement.</t>
+          <t>Separates what the manager controls from what they do not.</t>
         </is>
       </c>
       <c r="K120" s="12" t="inlineStr">
         <is>
-          <t>NH manager card</t>
+          <t>NH progress</t>
         </is>
       </c>
       <c r="L120" s="12" t="inlineStr">
         <is>
-          <t>M-18 / L-03</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="M120" s="12" t="inlineStr">
         <is>
-          <t>HM H-09</t>
-        </is>
-      </c>
-      <c r="N120" s="14" t="inlineStr">
-        <is>
-          <t>Gap closed</t>
+          <t>PRD 3.6</t>
+        </is>
+      </c>
+      <c r="N120" s="11" t="inlineStr">
+        <is>
+          <t>Mockup only</t>
         </is>
       </c>
     </row>
@@ -9575,32 +9599,32 @@
       </c>
       <c r="E121" s="10" t="inlineStr">
         <is>
-          <t>Rail</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>Quick confirm: add to 4 team channels</t>
+          <t>New hire name, start date, days remaining</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
         <is>
-          <t>Team membership</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="J121" s="10" t="inlineStr">
         <is>
-          <t>One tap for all four.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K121" s="10" t="inlineStr">
@@ -9610,17 +9634,17 @@
       </c>
       <c r="L121" s="10" t="inlineStr">
         <is>
-          <t>M-18</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M121" s="10" t="inlineStr">
         <is>
-          <t>HM H-12</t>
-        </is>
-      </c>
-      <c r="N121" s="14" t="inlineStr">
-        <is>
-          <t>Gap closed</t>
+          <t>HM Fields H-00.3</t>
+        </is>
+      </c>
+      <c r="N121" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -9647,32 +9671,32 @@
       </c>
       <c r="E122" s="12" t="inlineStr">
         <is>
-          <t>Rail</t>
+          <t>Blockers</t>
         </is>
       </c>
       <c r="F122" s="12" t="inlineStr">
         <is>
-          <t>PEX contact + Manager Onboarding Guide link</t>
+          <t>Blockers and escalation panel</t>
         </is>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>Contact + link</t>
+          <t>Display + action</t>
         </is>
       </c>
       <c r="H122" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I122" s="12" t="inlineStr">
         <is>
-          <t>Assigned PEX</t>
+          <t>Late/blocked tasks</t>
         </is>
       </c>
       <c r="J122" s="12" t="inlineStr">
         <is>
-          <t>Guide persists in the rail, not only in the notification.</t>
+          <t>Computed live: unordered computer, unassigned buddy near Day −3, overdue new hire tasks, blocked stack.</t>
         </is>
       </c>
       <c r="K122" s="12" t="inlineStr">
@@ -9682,17 +9706,17 @@
       </c>
       <c r="L122" s="12" t="inlineStr">
         <is>
-          <t>M-15</t>
+          <t>M-16</t>
         </is>
       </c>
       <c r="M122" s="12" t="inlineStr">
         <is>
-          <t>PRD S2-US12 AC2-3</t>
-        </is>
-      </c>
-      <c r="N122" s="15" t="inlineStr">
-        <is>
-          <t>Open — content</t>
+          <t>HM Fields H-00.8</t>
+        </is>
+      </c>
+      <c r="N122" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -9719,22 +9743,22 @@
       </c>
       <c r="E123" s="10" t="inlineStr">
         <is>
-          <t>Rail</t>
+          <t>Your tasks</t>
         </is>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>Link: how the two portals connect</t>
+          <t>Task cards with disposition badges</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
         <is>
-          <t>Link</t>
+          <t>Task cards ×7-8</t>
         </is>
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
@@ -9744,22 +9768,22 @@
       </c>
       <c r="J123" s="10" t="inlineStr">
         <is>
-          <t>Opens the handoff map.</t>
+          <t>Every card carries keep / exception-only / automate / remove / adds work.</t>
         </is>
       </c>
       <c r="K123" s="10" t="inlineStr">
         <is>
-          <t>Handoffs</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L123" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M-09</t>
         </is>
       </c>
       <c r="M123" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HM Task Disposition</t>
         </is>
       </c>
       <c r="N123" s="11" t="inlineStr">
@@ -9776,32 +9800,32 @@
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>H-00</t>
         </is>
       </c>
       <c r="C124" s="12" t="inlineStr">
         <is>
-          <t>Confirm the first-day details</t>
+          <t>New hire readiness view</t>
         </is>
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>#/hm/logistics</t>
+          <t>#/hm/</t>
         </is>
       </c>
       <c r="E124" s="12" t="inlineStr">
         <is>
-          <t>Blueprint</t>
+          <t>Your tasks</t>
         </is>
       </c>
       <c r="F124" s="12" t="inlineStr">
         <is>
-          <t>Where to go · parking · what to expect · dress code</t>
+          <t>Link to the subtraction review</t>
         </is>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
-          <t>Read-only ×4</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="H124" s="12" t="inlineStr">
@@ -9811,32 +9835,32 @@
       </c>
       <c r="I124" s="12" t="inlineStr">
         <is>
-          <t>NHO blueprint</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J124" s="12" t="inlineStr">
         <is>
-          <t>Read-only. Fixing them means fixing the blueprint, so every Denver starter benefits.</t>
+          <t>The argument screen for this side.</t>
         </is>
       </c>
       <c r="K124" s="12" t="inlineStr">
         <is>
-          <t>NH first-day card</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L124" s="12" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>M-09</t>
         </is>
       </c>
       <c r="M124" s="12" t="inlineStr">
         <is>
-          <t>HM OI-05</t>
-        </is>
-      </c>
-      <c r="N124" s="15" t="inlineStr">
-        <is>
-          <t>Open — BLOCKS BUILD</t>
+          <t>HM Task Disposition</t>
+        </is>
+      </c>
+      <c r="N124" s="11" t="inlineStr">
+        <is>
+          <t>Mockup device</t>
         </is>
       </c>
     </row>
@@ -9848,62 +9872,62 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>H-00</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Confirm the first-day details</t>
+          <t>New hire readiness view</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>#/hm/logistics</t>
+          <t>#/hm/</t>
         </is>
       </c>
       <c r="E125" s="10" t="inlineStr">
         <is>
-          <t>Manager input</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>Arrival time and where to come</t>
+          <t>Equipment orders table (identical to the new hire's)</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
         <is>
-          <t>Single line text</t>
+          <t>Display table</t>
         </is>
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr">
         <is>
-          <t>Blank</t>
+          <t>Equipment Orders</t>
         </is>
       </c>
       <c r="J125" s="10" t="inlineStr">
         <is>
-          <t>Feeds the new hire's first-day details card.</t>
+          <t>One source, both sides. Names who each item waits on.</t>
         </is>
       </c>
       <c r="K125" s="10" t="inlineStr">
         <is>
-          <t>NH first-day card</t>
+          <t>NH equipment</t>
         </is>
       </c>
       <c r="L125" s="10" t="inlineStr">
         <is>
-          <t>L-07</t>
+          <t>M-16 / L-04</t>
         </is>
       </c>
       <c r="M125" s="10" t="inlineStr">
         <is>
-          <t>HM Fields H-03.2</t>
+          <t>Live UAT portal</t>
         </is>
       </c>
       <c r="N125" s="14" t="inlineStr">
@@ -9920,67 +9944,67 @@
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>H-00</t>
         </is>
       </c>
       <c r="C126" s="12" t="inlineStr">
         <is>
-          <t>Confirm the first-day details</t>
+          <t>New hire readiness view</t>
         </is>
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>#/hm/logistics</t>
+          <t>#/hm/</t>
         </is>
       </c>
       <c r="E126" s="12" t="inlineStr">
         <is>
-          <t>Cover</t>
+          <t>New hire progress</t>
         </is>
       </c>
       <c r="F126" s="12" t="inlineStr">
         <is>
-          <t>Are you available on Day 1?</t>
+          <t>Task names + status, content withheld</t>
         </is>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Display ×5</t>
         </is>
       </c>
       <c r="H126" s="12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I126" s="12" t="inlineStr">
         <is>
-          <t>Assumed yes</t>
+          <t>New hire task records</t>
         </is>
       </c>
       <c r="J126" s="12" t="inlineStr">
         <is>
-          <t>'No' makes the proxy mandatory. Day 1 presence is a tracked measure.</t>
+          <t>Sensitive rows marked 'Detail hidden' with what is withheld named.</t>
         </is>
       </c>
       <c r="K126" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NH all tasks</t>
         </is>
       </c>
       <c r="L126" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M-03 / L-05</t>
         </is>
       </c>
       <c r="M126" s="12" t="inlineStr">
         <is>
-          <t>HM Fields H-03.7</t>
-        </is>
-      </c>
-      <c r="N126" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>HM OI-03</t>
+        </is>
+      </c>
+      <c r="N126" s="15" t="inlineStr">
+        <is>
+          <t>Open — BLOCKS BUILD</t>
         </is>
       </c>
     </row>
@@ -9992,67 +10016,67 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>H-00</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Confirm the first-day details</t>
+          <t>New hire readiness view</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>#/hm/logistics</t>
+          <t>#/hm/</t>
         </is>
       </c>
       <c r="E127" s="10" t="inlineStr">
         <is>
-          <t>Cover</t>
+          <t>Third party</t>
         </is>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>Day 1 proxy / delegate</t>
+          <t>PEX / EUT / CRE task status</t>
         </is>
       </c>
       <c r="G127" s="10" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Display ×3</t>
         </is>
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>Conditional</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr">
         <is>
-          <t>Blank</t>
+          <t>Task records across teams</t>
         </is>
       </c>
       <c r="J127" s="10" t="inlineStr">
         <is>
-          <t>Applies to this hire only, not permanently. What a proxy can see is undefined.</t>
+          <t>Badge print reflects whether the new hire submitted a photo.</t>
         </is>
       </c>
       <c r="K127" s="10" t="inlineStr">
         <is>
-          <t>NH first-day card</t>
+          <t>NH photo task</t>
         </is>
       </c>
       <c r="L127" s="10" t="inlineStr">
         <is>
-          <t>M-14</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M127" s="10" t="inlineStr">
         <is>
-          <t>HM OI-12 · PRD v1.4 proxy</t>
-        </is>
-      </c>
-      <c r="N127" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>PRD S2-US13 AC1</t>
+        </is>
+      </c>
+      <c r="N127" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -10064,67 +10088,67 @@
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>H-00</t>
         </is>
       </c>
       <c r="C128" s="12" t="inlineStr">
         <is>
-          <t>Confirm the first-day details</t>
+          <t>New hire readiness view</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>#/hm/logistics</t>
+          <t>#/hm/</t>
         </is>
       </c>
       <c r="E128" s="12" t="inlineStr">
         <is>
-          <t>Manager input</t>
+          <t>Rail</t>
         </is>
       </c>
       <c r="F128" s="12" t="inlineStr">
         <is>
-          <t>Team-specific note</t>
+          <t>New hire contact card</t>
         </is>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
-          <t>Multi line text</t>
+          <t>Contact card</t>
         </is>
       </c>
       <c r="H128" s="12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I128" s="12" t="inlineStr">
         <is>
-          <t>Blank</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="J128" s="12" t="inlineStr">
         <is>
-          <t>Optional. Also surfaces to the new hire.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K128" s="12" t="inlineStr">
         <is>
-          <t>NH first-day card</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L128" s="12" t="inlineStr">
         <is>
-          <t>L-07</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M128" s="12" t="inlineStr">
         <is>
-          <t>Assumption</t>
-        </is>
-      </c>
-      <c r="N128" s="11" t="inlineStr">
-        <is>
-          <t>Mockup only</t>
+          <t>HM spec</t>
+        </is>
+      </c>
+      <c r="N128" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -10136,27 +10160,27 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>H-00</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Order equipment for your new hire</t>
+          <t>New hire readiness view</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>#/hm/computer</t>
+          <t>#/hm/</t>
         </is>
       </c>
       <c r="E129" s="10" t="inlineStr">
         <is>
-          <t>Framing</t>
+          <t>Rail</t>
         </is>
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>This is an order, not a confirmation</t>
+          <t>Notice: the new hire already has your details</t>
         </is>
       </c>
       <c r="G129" s="10" t="inlineStr">
@@ -10171,32 +10195,32 @@
       </c>
       <c r="I129" s="10" t="inlineStr">
         <is>
-          <t>Live portal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J129" s="10" t="inlineStr">
         <is>
-          <t>Corrects the workbook baseline. Nothing ships until the manager acts.</t>
+          <t>Tells the manager they are contactable pre-Day 1, and that nothing sets a response expectation.</t>
         </is>
       </c>
       <c r="K129" s="10" t="inlineStr">
         <is>
-          <t>NH equipment table</t>
+          <t>NH rail</t>
         </is>
       </c>
       <c r="L129" s="10" t="inlineStr">
         <is>
-          <t>M-01</t>
+          <t>L-03</t>
         </is>
       </c>
       <c r="M129" s="10" t="inlineStr">
         <is>
-          <t>HM OI-24</t>
+          <t>HM OI-23</t>
         </is>
       </c>
       <c r="N129" s="15" t="inlineStr">
         <is>
-          <t>Open — BLOCKS BUILD</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -10208,67 +10232,67 @@
       </c>
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>H-00</t>
         </is>
       </c>
       <c r="C130" s="12" t="inlineStr">
         <is>
-          <t>Order equipment for your new hire</t>
+          <t>New hire readiness view</t>
         </is>
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>#/hm/computer</t>
+          <t>#/hm/</t>
         </is>
       </c>
       <c r="E130" s="12" t="inlineStr">
         <is>
-          <t>Selection</t>
+          <t>Rail</t>
         </is>
       </c>
       <c r="F130" s="12" t="inlineStr">
         <is>
-          <t>Three laptop options with lead times</t>
+          <t>Quick confirm: your contact details</t>
         </is>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>Radio ×3</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="H130" s="12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I130" s="12" t="inlineStr">
         <is>
-          <t>Catalogue</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="J130" s="12" t="inlineStr">
         <is>
-          <t>One option deliberately backordered so the late-delivery warning is visible.</t>
+          <t>One tap. Was a separate task; folded in because it needs no judgement.</t>
         </is>
       </c>
       <c r="K130" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NH manager card</t>
         </is>
       </c>
       <c r="L130" s="12" t="inlineStr">
         <is>
-          <t>M-17</t>
+          <t>M-18 / L-03</t>
         </is>
       </c>
       <c r="M130" s="12" t="inlineStr">
         <is>
-          <t>PRD S2-US07 AC3</t>
-        </is>
-      </c>
-      <c r="N130" s="15" t="inlineStr">
-        <is>
-          <t>Open — content needed</t>
+          <t>HM H-09</t>
+        </is>
+      </c>
+      <c r="N130" s="14" t="inlineStr">
+        <is>
+          <t>Gap closed</t>
         </is>
       </c>
     </row>
@@ -10280,67 +10304,67 @@
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>H-00</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Order equipment for your new hire</t>
+          <t>New hire readiness view</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>#/hm/computer</t>
+          <t>#/hm/</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Rail</t>
         </is>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t>Would arrive after the start date</t>
+          <t>Quick confirm: add to 4 team channels</t>
         </is>
       </c>
       <c r="G131" s="10" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr">
         <is>
-          <t>Lead time vs start</t>
+          <t>Team membership</t>
         </is>
       </c>
       <c r="J131" s="10" t="inlineStr">
         <is>
-          <t>Explains the loaner route and the notification to the equipment team.</t>
+          <t>One tap for all four.</t>
         </is>
       </c>
       <c r="K131" s="10" t="inlineStr">
         <is>
-          <t>NH equipment table</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L131" s="10" t="inlineStr">
         <is>
-          <t>M-17</t>
+          <t>M-18</t>
         </is>
       </c>
       <c r="M131" s="10" t="inlineStr">
         <is>
-          <t>PRD S2-US07 AC4</t>
-        </is>
-      </c>
-      <c r="N131" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>HM H-12</t>
+        </is>
+      </c>
+      <c r="N131" s="14" t="inlineStr">
+        <is>
+          <t>Gap closed</t>
         </is>
       </c>
     </row>
@@ -10352,67 +10376,67 @@
       </c>
       <c r="B132" s="12" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>H-00</t>
         </is>
       </c>
       <c r="C132" s="12" t="inlineStr">
         <is>
-          <t>Order equipment for your new hire</t>
+          <t>New hire readiness view</t>
         </is>
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>#/hm/computer</t>
+          <t>#/hm/</t>
         </is>
       </c>
       <c r="E132" s="12" t="inlineStr">
         <is>
-          <t>Override</t>
+          <t>Rail</t>
         </is>
       </c>
       <c r="F132" s="12" t="inlineStr">
         <is>
-          <t>Reason (mandatory on the late option)</t>
+          <t>PEX contact + Manager Onboarding Guide link</t>
         </is>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>Multi line text</t>
+          <t>Contact + link</t>
         </is>
       </c>
       <c r="H132" s="12" t="inlineStr">
         <is>
-          <t>Conditional</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I132" s="12" t="inlineStr">
         <is>
-          <t>Blank</t>
+          <t>Assigned PEX</t>
         </is>
       </c>
       <c r="J132" s="12" t="inlineStr">
         <is>
-          <t>Recorded with the order and shown to the new hire.</t>
+          <t>Guide persists in the rail, not only in the notification.</t>
         </is>
       </c>
       <c r="K132" s="12" t="inlineStr">
         <is>
-          <t>NH notification</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L132" s="12" t="inlineStr">
         <is>
-          <t>M-01</t>
+          <t>M-15</t>
         </is>
       </c>
       <c r="M132" s="12" t="inlineStr">
         <is>
-          <t>PRD S2-US07 edge 1</t>
-        </is>
-      </c>
-      <c r="N132" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>PRD S2-US12 AC2-3</t>
+        </is>
+      </c>
+      <c r="N132" s="15" t="inlineStr">
+        <is>
+          <t>Open — content</t>
         </is>
       </c>
     </row>
@@ -10424,67 +10448,67 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>H-00</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Order equipment for your new hire</t>
+          <t>New hire readiness view</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>#/hm/computer</t>
+          <t>#/hm/</t>
         </is>
       </c>
       <c r="E133" s="10" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>Rail</t>
         </is>
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t>Accessories and phone are explicitly not the manager's</t>
+          <t>Link: how the two portals connect</t>
         </is>
       </c>
       <c r="G133" s="10" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I133" s="10" t="inlineStr">
         <is>
-          <t>Live portal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J133" s="10" t="inlineStr">
         <is>
-          <t>States the boundary rather than leaving it implied.</t>
+          <t>Opens the handoff map.</t>
         </is>
       </c>
       <c r="K133" s="10" t="inlineStr">
         <is>
-          <t>NH equipment</t>
+          <t>Handoffs</t>
         </is>
       </c>
       <c r="L133" s="10" t="inlineStr">
         <is>
-          <t>A-40 / M-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M133" s="10" t="inlineStr">
         <is>
-          <t>Merge Analysis 11</t>
-        </is>
-      </c>
-      <c r="N133" s="14" t="inlineStr">
-        <is>
-          <t>Gap closed</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N133" s="11" t="inlineStr">
+        <is>
+          <t>Mockup device</t>
         </is>
       </c>
     </row>
@@ -10496,32 +10520,32 @@
       </c>
       <c r="B134" s="12" t="inlineStr">
         <is>
-          <t>H-05</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="C134" s="12" t="inlineStr">
         <is>
-          <t>Confirm the application stack</t>
+          <t>Confirm the first-day details</t>
         </is>
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>#/hm/software</t>
+          <t>#/hm/logistics</t>
         </is>
       </c>
       <c r="E134" s="12" t="inlineStr">
         <is>
-          <t>Blocked state</t>
+          <t>Blueprint</t>
         </is>
       </c>
       <c r="F134" s="12" t="inlineStr">
         <is>
-          <t>'There is no default stack to show you'</t>
+          <t>Where to go · parking · what to expect · dress code</t>
         </is>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Read-only ×4</t>
         </is>
       </c>
       <c r="H134" s="12" t="inlineStr">
@@ -10531,27 +10555,27 @@
       </c>
       <c r="I134" s="12" t="inlineStr">
         <is>
-          <t>Persona (unresolved)</t>
+          <t>NHO blueprint</t>
         </is>
       </c>
       <c r="J134" s="12" t="inlineStr">
         <is>
-          <t>The screen is drawn as it behaves today, not as intended.</t>
+          <t>Read-only. Fixing them means fixing the blueprint, so every Denver starter benefits.</t>
         </is>
       </c>
       <c r="K134" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NH first-day card</t>
         </is>
       </c>
       <c r="L134" s="12" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="M134" s="12" t="inlineStr">
         <is>
-          <t>HM OI-04</t>
+          <t>HM OI-05</t>
         </is>
       </c>
       <c r="N134" s="15" t="inlineStr">
@@ -10568,67 +10592,67 @@
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>H-05</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>Confirm the application stack</t>
+          <t>Confirm the first-day details</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>#/hm/software</t>
+          <t>#/hm/logistics</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
         <is>
-          <t>Default stack</t>
+          <t>Manager input</t>
         </is>
       </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>Persona default (renders empty)</t>
+          <t>Arrival time and where to come</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
         <is>
-          <t>Display list</t>
+          <t>Single line text</t>
         </is>
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr">
         <is>
-          <t>Persona</t>
+          <t>Blank</t>
         </is>
       </c>
       <c r="J135" s="10" t="inlineStr">
         <is>
-          <t>Empty because no full persona list exists in the platform.</t>
+          <t>Feeds the new hire's first-day details card.</t>
         </is>
       </c>
       <c r="K135" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NH first-day card</t>
         </is>
       </c>
       <c r="L135" s="10" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>L-07</t>
         </is>
       </c>
       <c r="M135" s="10" t="inlineStr">
         <is>
-          <t>PRD S2-US16 AC1</t>
-        </is>
-      </c>
-      <c r="N135" s="15" t="inlineStr">
-        <is>
-          <t>Open — BLOCKS BUILD</t>
+          <t>HM Fields H-03.2</t>
+        </is>
+      </c>
+      <c r="N135" s="14" t="inlineStr">
+        <is>
+          <t>Gap closed</t>
         </is>
       </c>
     </row>
@@ -10640,47 +10664,47 @@
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t>H-05</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="C136" s="12" t="inlineStr">
         <is>
-          <t>Confirm the application stack</t>
+          <t>Confirm the first-day details</t>
         </is>
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>#/hm/software</t>
+          <t>#/hm/logistics</t>
         </is>
       </c>
       <c r="E136" s="12" t="inlineStr">
         <is>
-          <t>Additions</t>
+          <t>Cover</t>
         </is>
       </c>
       <c r="F136" s="12" t="inlineStr">
         <is>
-          <t>Add applications by hand (catalogue items only)</t>
+          <t>Are you available on Day 1?</t>
         </is>
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
-          <t>Checkbox ×8</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="H136" s="12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I136" s="12" t="inlineStr">
         <is>
-          <t>Blank</t>
+          <t>Assumed yes</t>
         </is>
       </c>
       <c r="J136" s="12" t="inlineStr">
         <is>
-          <t>Each raises its own request with its own approval flow.</t>
+          <t>'No' makes the proxy mandatory. Day 1 presence is a tracked measure.</t>
         </is>
       </c>
       <c r="K136" s="12" t="inlineStr">
@@ -10690,12 +10714,12 @@
       </c>
       <c r="L136" s="12" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M136" s="12" t="inlineStr">
         <is>
-          <t>PRD S2-US16 AC2-3</t>
+          <t>HM Fields H-03.7</t>
         </is>
       </c>
       <c r="N136" s="13" t="inlineStr">
@@ -10712,62 +10736,62 @@
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>H-05</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Confirm the application stack</t>
+          <t>Confirm the first-day details</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>#/hm/software</t>
+          <t>#/hm/logistics</t>
         </is>
       </c>
       <c r="E137" s="10" t="inlineStr">
         <is>
-          <t>Open question</t>
+          <t>Cover</t>
         </is>
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>May a manager remove from the default?</t>
+          <t>Day 1 proxy / delegate</t>
         </is>
       </c>
       <c r="G137" s="10" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Conditional</t>
         </is>
       </c>
       <c r="I137" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Blank</t>
         </is>
       </c>
       <c r="J137" s="10" t="inlineStr">
         <is>
-          <t>Requirements cover additions in detail and never mention removals.</t>
+          <t>Applies to this hire only, not permanently. What a proxy can see is undefined.</t>
         </is>
       </c>
       <c r="K137" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NH first-day card</t>
         </is>
       </c>
       <c r="L137" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M-14</t>
         </is>
       </c>
       <c r="M137" s="10" t="inlineStr">
         <is>
-          <t>HM OI-08</t>
+          <t>HM OI-12 · PRD v1.4 proxy</t>
         </is>
       </c>
       <c r="N137" s="15" t="inlineStr">
@@ -10784,67 +10808,67 @@
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
-          <t>H-07</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="C138" s="12" t="inlineStr">
         <is>
-          <t>Choose an onboarding buddy</t>
+          <t>Confirm the first-day details</t>
         </is>
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>#/hm/buddy</t>
+          <t>#/hm/logistics</t>
         </is>
       </c>
       <c r="E138" s="12" t="inlineStr">
         <is>
-          <t>Conflict</t>
+          <t>Manager input</t>
         </is>
       </c>
       <c r="F138" s="12" t="inlineStr">
         <is>
-          <t>Buddy visibility rule switch (assignment vs 72h)</t>
+          <t>Team-specific note</t>
         </is>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>Prototype control</t>
+          <t>Multi line text</t>
         </is>
       </c>
       <c r="H138" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I138" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Blank</t>
         </is>
       </c>
       <c r="J138" s="12" t="inlineStr">
         <is>
-          <t>Implements both contradictory rules so the difference is arguable.</t>
+          <t>Optional. Also surfaces to the new hire.</t>
         </is>
       </c>
       <c r="K138" s="12" t="inlineStr">
         <is>
-          <t>NH people rail</t>
+          <t>NH first-day card</t>
         </is>
       </c>
       <c r="L138" s="12" t="inlineStr">
         <is>
-          <t>L-01</t>
+          <t>L-07</t>
         </is>
       </c>
       <c r="M138" s="12" t="inlineStr">
         <is>
-          <t>HM OI-22</t>
-        </is>
-      </c>
-      <c r="N138" s="16" t="inlineStr">
-        <is>
-          <t>CONFLICT — BLOCKS BUILD</t>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="N138" s="11" t="inlineStr">
+        <is>
+          <t>Mockup only</t>
         </is>
       </c>
     </row>
@@ -10856,67 +10880,67 @@
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>H-07</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Choose an onboarding buddy</t>
+          <t>Order equipment for your new hire</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>#/hm/buddy</t>
+          <t>#/hm/computer</t>
         </is>
       </c>
       <c r="E139" s="10" t="inlineStr">
         <is>
-          <t>Suggestion</t>
+          <t>Framing</t>
         </is>
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>Suggested buddy with current load</t>
+          <t>This is an order, not a confirmation</t>
         </is>
       </c>
       <c r="G139" s="10" t="inlineStr">
         <is>
-          <t>Display + action</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr">
         <is>
-          <t>Suggestion engine</t>
+          <t>Live portal</t>
         </is>
       </c>
       <c r="J139" s="10" t="inlineStr">
         <is>
-          <t>One tap when the manager agrees.</t>
+          <t>Corrects the workbook baseline. Nothing ships until the manager acts.</t>
         </is>
       </c>
       <c r="K139" s="10" t="inlineStr">
         <is>
-          <t>NH people rail</t>
+          <t>NH equipment table</t>
         </is>
       </c>
       <c r="L139" s="10" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>M-01</t>
         </is>
       </c>
       <c r="M139" s="10" t="inlineStr">
         <is>
-          <t>PRD S2-US18 AC1</t>
+          <t>HM OI-24</t>
         </is>
       </c>
       <c r="N139" s="15" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Open — BLOCKS BUILD</t>
         </is>
       </c>
     </row>
@@ -10928,47 +10952,47 @@
       </c>
       <c r="B140" s="12" t="inlineStr">
         <is>
-          <t>H-07</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C140" s="12" t="inlineStr">
         <is>
-          <t>Choose an onboarding buddy</t>
+          <t>Order equipment for your new hire</t>
         </is>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>#/hm/buddy</t>
+          <t>#/hm/computer</t>
         </is>
       </c>
       <c r="E140" s="12" t="inlineStr">
         <is>
-          <t>Privacy</t>
+          <t>Selection</t>
         </is>
       </c>
       <c r="F140" s="12" t="inlineStr">
         <is>
-          <t>Why this person was suggested is withheld</t>
+          <t>Three laptop options with lead times</t>
         </is>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Radio ×3</t>
         </is>
       </c>
       <c r="H140" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I140" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Catalogue</t>
         </is>
       </c>
       <c r="J140" s="12" t="inlineStr">
         <is>
-          <t>The criteria include a performance signal; surfacing it would show an inference about another employee.</t>
+          <t>One option deliberately backordered so the late-delivery warning is visible.</t>
         </is>
       </c>
       <c r="K140" s="12" t="inlineStr">
@@ -10978,17 +11002,17 @@
       </c>
       <c r="L140" s="12" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>M-17</t>
         </is>
       </c>
       <c r="M140" s="12" t="inlineStr">
         <is>
-          <t>HM OI-10</t>
+          <t>PRD S2-US07 AC3</t>
         </is>
       </c>
       <c r="N140" s="15" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Open — content needed</t>
         </is>
       </c>
     </row>
@@ -11000,67 +11024,67 @@
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>H-07</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Choose an onboarding buddy</t>
+          <t>Order equipment for your new hire</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>#/hm/buddy</t>
+          <t>#/hm/computer</t>
         </is>
       </c>
       <c r="E141" s="10" t="inlineStr">
         <is>
-          <t>Alternatives</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t>Filterable alternatives with capacity warning</t>
+          <t>Would arrive after the start date</t>
         </is>
       </c>
       <c r="G141" s="10" t="inlineStr">
         <is>
-          <t>List + action</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H141" s="10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr">
         <is>
-          <t>Buddy pool</t>
+          <t>Lead time vs start</t>
         </is>
       </c>
       <c r="J141" s="10" t="inlineStr">
         <is>
-          <t>Warning at 3 concurrent — the limit is invented because the policy is undefined.</t>
+          <t>Explains the loaner route and the notification to the equipment team.</t>
         </is>
       </c>
       <c r="K141" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NH equipment table</t>
         </is>
       </c>
       <c r="L141" s="10" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>M-17</t>
         </is>
       </c>
       <c r="M141" s="10" t="inlineStr">
         <is>
-          <t>HM OI-10</t>
-        </is>
-      </c>
-      <c r="N141" s="15" t="inlineStr">
-        <is>
-          <t>Open — content needed</t>
+          <t>PRD S2-US07 AC4</t>
+        </is>
+      </c>
+      <c r="N141" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -11072,62 +11096,62 @@
       </c>
       <c r="B142" s="12" t="inlineStr">
         <is>
-          <t>H-07</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C142" s="12" t="inlineStr">
         <is>
-          <t>Choose an onboarding buddy</t>
+          <t>Order equipment for your new hire</t>
         </is>
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>#/hm/buddy</t>
+          <t>#/hm/computer</t>
         </is>
       </c>
       <c r="E142" s="12" t="inlineStr">
         <is>
-          <t>Consequence</t>
+          <t>Override</t>
         </is>
       </c>
       <c r="F142" s="12" t="inlineStr">
         <is>
-          <t>What happens now: assigned → notified → visible → changeable</t>
+          <t>Reason (mandatory on the late option)</t>
         </is>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
-          <t>Display ×4</t>
+          <t>Multi line text</t>
         </is>
       </c>
       <c r="H142" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Conditional</t>
         </is>
       </c>
       <c r="I142" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Blank</t>
         </is>
       </c>
       <c r="J142" s="12" t="inlineStr">
         <is>
-          <t>Makes the downstream effects of the assignment visible.</t>
+          <t>Recorded with the order and shown to the new hire.</t>
         </is>
       </c>
       <c r="K142" s="12" t="inlineStr">
         <is>
-          <t>NH people rail</t>
+          <t>NH notification</t>
         </is>
       </c>
       <c r="L142" s="12" t="inlineStr">
         <is>
-          <t>L-01 / L-09</t>
+          <t>M-01</t>
         </is>
       </c>
       <c r="M142" s="12" t="inlineStr">
         <is>
-          <t>PRD S2-US18 AC2-3</t>
+          <t>PRD S2-US07 edge 1</t>
         </is>
       </c>
       <c r="N142" s="13" t="inlineStr">
@@ -11144,67 +11168,67 @@
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>H-08</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Set up their first day</t>
+          <t>Order equipment for your new hire</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>#/hm/calendar</t>
+          <t>#/hm/computer</t>
         </is>
       </c>
       <c r="E143" s="10" t="inlineStr">
         <is>
-          <t>Auto hold</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>Day 1 one-to-one — placed automatically, cannot be deleted</t>
+          <t>Accessories and phone are explicitly not the manager's</t>
         </is>
       </c>
       <c r="G143" s="10" t="inlineStr">
         <is>
-          <t>Calendar hold</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H143" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Live portal</t>
         </is>
       </c>
       <c r="J143" s="10" t="inlineStr">
         <is>
-          <t>One hour immediately after the cohort lunch. Reschedule only.</t>
+          <t>States the boundary rather than leaving it implied.</t>
         </is>
       </c>
       <c r="K143" s="10" t="inlineStr">
         <is>
-          <t>Outlook</t>
+          <t>NH equipment</t>
         </is>
       </c>
       <c r="L143" s="10" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>A-40 / M-01</t>
         </is>
       </c>
       <c r="M143" s="10" t="inlineStr">
         <is>
-          <t>BTR activity 17</t>
-        </is>
-      </c>
-      <c r="N143" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>Merge Analysis 11</t>
+        </is>
+      </c>
+      <c r="N143" s="14" t="inlineStr">
+        <is>
+          <t>Gap closed</t>
         </is>
       </c>
     </row>
@@ -11216,32 +11240,32 @@
       </c>
       <c r="B144" s="12" t="inlineStr">
         <is>
-          <t>H-08</t>
+          <t>H-05</t>
         </is>
       </c>
       <c r="C144" s="12" t="inlineStr">
         <is>
-          <t>Set up their first day</t>
+          <t>Confirm the application stack</t>
         </is>
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>#/hm/calendar</t>
+          <t>#/hm/software</t>
         </is>
       </c>
       <c r="E144" s="12" t="inlineStr">
         <is>
-          <t>Blueprint hold</t>
+          <t>Blocked state</t>
         </is>
       </c>
       <c r="F144" s="12" t="inlineStr">
         <is>
-          <t>New Hire Orientation — read-only</t>
+          <t>'There is no default stack to show you'</t>
         </is>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
-          <t>Calendar hold</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H144" s="12" t="inlineStr">
@@ -11251,12 +11275,12 @@
       </c>
       <c r="I144" s="12" t="inlineStr">
         <is>
-          <t>NHO blueprint</t>
+          <t>Persona (unresolved)</t>
         </is>
       </c>
       <c r="J144" s="12" t="inlineStr">
         <is>
-          <t>PEX owns it; the manager cannot move it.</t>
+          <t>The screen is drawn as it behaves today, not as intended.</t>
         </is>
       </c>
       <c r="K144" s="12" t="inlineStr">
@@ -11266,17 +11290,17 @@
       </c>
       <c r="L144" s="12" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="M144" s="12" t="inlineStr">
         <is>
-          <t>PRD S3-US06</t>
-        </is>
-      </c>
-      <c r="N144" s="13" t="inlineStr">
-        <is>
-          <t>Aligned</t>
+          <t>HM OI-04</t>
+        </is>
+      </c>
+      <c r="N144" s="15" t="inlineStr">
+        <is>
+          <t>Open — BLOCKS BUILD</t>
         </is>
       </c>
     </row>
@@ -11288,47 +11312,47 @@
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>H-08</t>
+          <t>H-05</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>Set up their first day</t>
+          <t>Confirm the application stack</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>#/hm/calendar</t>
+          <t>#/hm/software</t>
         </is>
       </c>
       <c r="E145" s="10" t="inlineStr">
         <is>
-          <t>Suggested</t>
+          <t>Default stack</t>
         </is>
       </c>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t>Team intro · buddy check-in · IT setup window</t>
+          <t>Persona default (renders empty)</t>
         </is>
       </c>
       <c r="G145" s="10" t="inlineStr">
         <is>
-          <t>Checkbox ×3</t>
+          <t>Display list</t>
         </is>
       </c>
       <c r="H145" s="10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I145" s="10" t="inlineStr">
         <is>
-          <t>Blueprint suggestion</t>
+          <t>Persona</t>
         </is>
       </c>
       <c r="J145" s="10" t="inlineStr">
         <is>
-          <t>Accepted one at a time today. If auto-created, the screen becomes a glance.</t>
+          <t>Empty because no full persona list exists in the platform.</t>
         </is>
       </c>
       <c r="K145" s="10" t="inlineStr">
@@ -11338,12 +11362,12 @@
       </c>
       <c r="L145" s="10" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="M145" s="10" t="inlineStr">
         <is>
-          <t>HM OI-13</t>
+          <t>PRD S2-US16 AC1</t>
         </is>
       </c>
       <c r="N145" s="15" t="inlineStr">
@@ -11360,62 +11384,62 @@
       </c>
       <c r="B146" s="12" t="inlineStr">
         <is>
-          <t>H-10</t>
+          <t>H-05</t>
         </is>
       </c>
       <c r="C146" s="12" t="inlineStr">
         <is>
-          <t>Send a welcome note</t>
+          <t>Confirm the application stack</t>
         </is>
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>#/hm/welcome</t>
+          <t>#/hm/software</t>
         </is>
       </c>
       <c r="E146" s="12" t="inlineStr">
         <is>
-          <t>Recipient</t>
+          <t>Additions</t>
         </is>
       </c>
       <c r="F146" s="12" t="inlineStr">
         <is>
-          <t>To — the new hire's personal email (read-only)</t>
+          <t>Add applications by hand (catalogue items only)</t>
         </is>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Checkbox ×8</t>
         </is>
       </c>
       <c r="H146" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I146" s="12" t="inlineStr">
         <is>
-          <t>Personal details task</t>
+          <t>Blank</t>
         </is>
       </c>
       <c r="J146" s="12" t="inlineStr">
         <is>
-          <t>Depends on the new hire having supplied it.</t>
+          <t>Each raises its own request with its own approval flow.</t>
         </is>
       </c>
       <c r="K146" s="12" t="inlineStr">
         <is>
-          <t>NH personal details</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L146" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="M146" s="12" t="inlineStr">
         <is>
-          <t>HM Fields H-10.1</t>
+          <t>PRD S2-US16 AC2-3</t>
         </is>
       </c>
       <c r="N146" s="13" t="inlineStr">
@@ -11432,67 +11456,67 @@
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>H-10</t>
+          <t>H-05</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>Send a welcome note</t>
+          <t>Confirm the application stack</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>#/hm/welcome</t>
+          <t>#/hm/software</t>
         </is>
       </c>
       <c r="E147" s="10" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Open question</t>
         </is>
       </c>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t>Standard welcome, pre-filled and editable</t>
+          <t>May a manager remove from the default?</t>
         </is>
       </c>
       <c r="G147" s="10" t="inlineStr">
         <is>
-          <t>Rich text</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H147" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I147" s="10" t="inlineStr">
         <is>
-          <t>Boilerplate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J147" s="10" t="inlineStr">
         <is>
-          <t>Written for the manager, not by them.</t>
+          <t>Requirements cover additions in detail and never mention removals.</t>
         </is>
       </c>
       <c r="K147" s="10" t="inlineStr">
         <is>
-          <t>NH landing</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L147" s="10" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M147" s="10" t="inlineStr">
         <is>
-          <t>HM Fields H-10.2</t>
+          <t>HM OI-08</t>
         </is>
       </c>
       <c r="N147" s="15" t="inlineStr">
         <is>
-          <t>Open — see Alignment G-13</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -11504,67 +11528,67 @@
       </c>
       <c r="B148" s="12" t="inlineStr">
         <is>
-          <t>H-10</t>
+          <t>H-07</t>
         </is>
       </c>
       <c r="C148" s="12" t="inlineStr">
         <is>
-          <t>Send a welcome note</t>
+          <t>Choose an onboarding buddy</t>
         </is>
       </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>#/hm/welcome</t>
+          <t>#/hm/buddy</t>
         </is>
       </c>
       <c r="E148" s="12" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Conflict</t>
         </is>
       </c>
       <c r="F148" s="12" t="inlineStr">
         <is>
-          <t>Your personal message</t>
+          <t>Buddy visibility rule switch (assignment vs 72h)</t>
         </is>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
-          <t>Multi line text</t>
+          <t>Prototype control</t>
         </is>
       </c>
       <c r="H148" s="12" t="inlineStr">
         <is>
-          <t>Recommended</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I148" s="12" t="inlineStr">
         <is>
-          <t>Blank</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J148" s="12" t="inlineStr">
         <is>
-          <t>The only part that genuinely needs the manager.</t>
+          <t>Implements both contradictory rules so the difference is arguable.</t>
         </is>
       </c>
       <c r="K148" s="12" t="inlineStr">
         <is>
-          <t>NH landing</t>
+          <t>NH people rail</t>
         </is>
       </c>
       <c r="L148" s="12" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>L-01</t>
         </is>
       </c>
       <c r="M148" s="12" t="inlineStr">
         <is>
-          <t>HM Fields H-10.3</t>
-        </is>
-      </c>
-      <c r="N148" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>HM OI-22</t>
+        </is>
+      </c>
+      <c r="N148" s="16" t="inlineStr">
+        <is>
+          <t>CONFLICT — BLOCKS BUILD</t>
         </is>
       </c>
     </row>
@@ -11576,62 +11600,62 @@
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>H-10</t>
+          <t>H-07</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Send a welcome note</t>
+          <t>Choose an onboarding buddy</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>#/hm/welcome</t>
+          <t>#/hm/buddy</t>
         </is>
       </c>
       <c r="E149" s="10" t="inlineStr">
         <is>
-          <t>System block</t>
+          <t>Suggestion</t>
         </is>
       </c>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>'What to expect in your first week' — read-only</t>
+          <t>Suggested buddy with current load</t>
         </is>
       </c>
       <c r="G149" s="10" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Display + action</t>
         </is>
       </c>
       <c r="H149" s="10" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I149" s="10" t="inlineStr">
         <is>
-          <t>New hire's task list</t>
+          <t>Suggestion engine</t>
         </is>
       </c>
       <c r="J149" s="10" t="inlineStr">
         <is>
-          <t>Generated, not written. Manager cannot edit it.</t>
+          <t>One tap when the manager agrees.</t>
         </is>
       </c>
       <c r="K149" s="10" t="inlineStr">
         <is>
-          <t>NH task list</t>
+          <t>NH people rail</t>
         </is>
       </c>
       <c r="L149" s="10" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="M149" s="10" t="inlineStr">
         <is>
-          <t>HM Fields H-10.4</t>
+          <t>PRD S2-US18 AC1</t>
         </is>
       </c>
       <c r="N149" s="15" t="inlineStr">
@@ -11648,27 +11672,27 @@
       </c>
       <c r="B150" s="12" t="inlineStr">
         <is>
-          <t>H-10</t>
+          <t>H-07</t>
         </is>
       </c>
       <c r="C150" s="12" t="inlineStr">
         <is>
-          <t>Send a welcome note</t>
+          <t>Choose an onboarding buddy</t>
         </is>
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>#/hm/welcome</t>
+          <t>#/hm/buddy</t>
         </is>
       </c>
       <c r="E150" s="12" t="inlineStr">
         <is>
-          <t>Sequencing</t>
+          <t>Privacy</t>
         </is>
       </c>
       <c r="F150" s="12" t="inlineStr">
         <is>
-          <t>Should land before the introduction is requested</t>
+          <t>Why this person was suggested is withheld</t>
         </is>
       </c>
       <c r="G150" s="12" t="inlineStr">
@@ -11688,22 +11712,22 @@
       </c>
       <c r="J150" s="12" t="inlineStr">
         <is>
-          <t>Stated, not enforced. Three welcome messages compete for the same week.</t>
+          <t>The criteria include a performance signal; surfacing it would show an inference about another employee.</t>
         </is>
       </c>
       <c r="K150" s="12" t="inlineStr">
         <is>
-          <t>NH introduction</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L150" s="12" t="inlineStr">
         <is>
-          <t>L-08</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="M150" s="12" t="inlineStr">
         <is>
-          <t>Merge Analysis 7</t>
+          <t>HM OI-10</t>
         </is>
       </c>
       <c r="N150" s="15" t="inlineStr">
@@ -11720,47 +11744,47 @@
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>H-11</t>
+          <t>H-07</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Name who they should meet</t>
+          <t>Choose an onboarding buddy</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>#/hm/network</t>
+          <t>#/hm/buddy</t>
         </is>
       </c>
       <c r="E151" s="10" t="inlineStr">
         <is>
-          <t>Framing</t>
+          <t>Alternatives</t>
         </is>
       </c>
       <c r="F151" s="10" t="inlineStr">
         <is>
-          <t>This adds to your workload — the only item that does</t>
+          <t>Filterable alternatives with capacity warning</t>
         </is>
       </c>
       <c r="G151" s="10" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>List + action</t>
         </is>
       </c>
       <c r="H151" s="10" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I151" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Buddy pool</t>
         </is>
       </c>
       <c r="J151" s="10" t="inlineStr">
         <is>
-          <t>Stated on the screen rather than hidden.</t>
+          <t>Warning at 3 concurrent — the limit is invented because the policy is undefined.</t>
         </is>
       </c>
       <c r="K151" s="10" t="inlineStr">
@@ -11770,17 +11794,17 @@
       </c>
       <c r="L151" s="10" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="M151" s="10" t="inlineStr">
         <is>
-          <t>HM OI-26</t>
+          <t>HM OI-10</t>
         </is>
       </c>
       <c r="N151" s="15" t="inlineStr">
         <is>
-          <t>Open — needs decision</t>
+          <t>Open — content needed</t>
         </is>
       </c>
     </row>
@@ -11792,67 +11816,67 @@
       </c>
       <c r="B152" s="12" t="inlineStr">
         <is>
-          <t>H-11</t>
+          <t>H-07</t>
         </is>
       </c>
       <c r="C152" s="12" t="inlineStr">
         <is>
-          <t>Name who they should meet</t>
+          <t>Choose an onboarding buddy</t>
         </is>
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>#/hm/network</t>
+          <t>#/hm/buddy</t>
         </is>
       </c>
       <c r="E152" s="12" t="inlineStr">
         <is>
-          <t>Selection</t>
+          <t>Consequence</t>
         </is>
       </c>
       <c r="F152" s="12" t="inlineStr">
         <is>
-          <t>Suggested people, pickable (7 in the pool)</t>
+          <t>What happens now: assigned → notified → visible → changeable</t>
         </is>
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
-          <t>Checkbox list</t>
+          <t>Display ×4</t>
         </is>
       </c>
       <c r="H152" s="12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I152" s="12" t="inlineStr">
         <is>
-          <t>Org data</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J152" s="12" t="inlineStr">
         <is>
-          <t>Five suggested with draft reasons; two unsuggested with none.</t>
+          <t>Makes the downstream effects of the assignment visible.</t>
         </is>
       </c>
       <c r="K152" s="12" t="inlineStr">
         <is>
-          <t>NH network</t>
+          <t>NH people rail</t>
         </is>
       </c>
       <c r="L152" s="12" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>L-01 / L-09</t>
         </is>
       </c>
       <c r="M152" s="12" t="inlineStr">
         <is>
-          <t>HM H-11</t>
-        </is>
-      </c>
-      <c r="N152" s="15" t="inlineStr">
-        <is>
-          <t>Open — see Alignment G-12</t>
+          <t>PRD S2-US18 AC2-3</t>
+        </is>
+      </c>
+      <c r="N152" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -11864,67 +11888,67 @@
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>H-11</t>
+          <t>H-08</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>Name who they should meet</t>
+          <t>Set up their first day</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>#/hm/network</t>
+          <t>#/hm/calendar</t>
         </is>
       </c>
       <c r="E153" s="10" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Auto hold</t>
         </is>
       </c>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>Why should they meet this person? (required per person)</t>
+          <t>Day 1 one-to-one — placed automatically, cannot be deleted</t>
         </is>
       </c>
       <c r="G153" s="10" t="inlineStr">
         <is>
-          <t>Multi line text</t>
+          <t>Calendar hold</t>
         </is>
       </c>
       <c r="H153" s="10" t="inlineStr">
         <is>
-          <t>Yes per person</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr">
         <is>
-          <t>Draft text</t>
+          <t>System</t>
         </is>
       </c>
       <c r="J153" s="10" t="inlineStr">
         <is>
-          <t>Editable draft. Reaches the new hire verbatim.</t>
+          <t>One hour immediately after the cohort lunch. Reschedule only.</t>
         </is>
       </c>
       <c r="K153" s="10" t="inlineStr">
         <is>
-          <t>NH network</t>
+          <t>Outlook</t>
         </is>
       </c>
       <c r="L153" s="10" t="inlineStr">
         <is>
-          <t>L-06</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="M153" s="10" t="inlineStr">
         <is>
-          <t>1:1 with platform owner</t>
-        </is>
-      </c>
-      <c r="N153" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>BTR activity 17</t>
+        </is>
+      </c>
+      <c r="N153" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -11936,67 +11960,67 @@
       </c>
       <c r="B154" s="12" t="inlineStr">
         <is>
-          <t>H-11</t>
+          <t>H-08</t>
         </is>
       </c>
       <c r="C154" s="12" t="inlineStr">
         <is>
-          <t>Name who they should meet</t>
+          <t>Set up their first day</t>
         </is>
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>#/hm/network</t>
+          <t>#/hm/calendar</t>
         </is>
       </c>
       <c r="E154" s="12" t="inlineStr">
         <is>
-          <t>Threshold</t>
+          <t>Blueprint hold</t>
         </is>
       </c>
       <c r="F154" s="12" t="inlineStr">
         <is>
-          <t>At least five people, each with a reason</t>
+          <t>New Hire Orientation — read-only</t>
         </is>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Calendar hold</t>
         </is>
       </c>
       <c r="H154" s="12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I154" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NHO blueprint</t>
         </is>
       </c>
       <c r="J154" s="12" t="inlineStr">
         <is>
-          <t>Submit gated at five. Nobody has said what happens at three or twelve.</t>
+          <t>PEX owns it; the manager cannot move it.</t>
         </is>
       </c>
       <c r="K154" s="12" t="inlineStr">
         <is>
-          <t>NH network</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L154" s="12" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="M154" s="12" t="inlineStr">
         <is>
-          <t>1:1 with platform owner</t>
-        </is>
-      </c>
-      <c r="N154" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>PRD S3-US06</t>
+        </is>
+      </c>
+      <c r="N154" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -12008,67 +12032,67 @@
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>H-11</t>
+          <t>H-08</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Name who they should meet</t>
+          <t>Set up their first day</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>#/hm/network</t>
+          <t>#/hm/calendar</t>
         </is>
       </c>
       <c r="E155" s="10" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Suggested</t>
         </is>
       </c>
       <c r="F155" s="10" t="inlineStr">
         <is>
-          <t>Each named person is notified</t>
+          <t>Team intro · buddy check-in · IT setup window</t>
         </is>
       </c>
       <c r="G155" s="10" t="inlineStr">
         <is>
-          <t>Behaviour</t>
+          <t>Checkbox ×3</t>
         </is>
       </c>
       <c r="H155" s="10" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I155" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Blueprint suggestion</t>
         </is>
       </c>
       <c r="J155" s="10" t="inlineStr">
         <is>
-          <t>Shown as an effect; content of the notification not specified.</t>
+          <t>Accepted one at a time today. If auto-created, the screen becomes a glance.</t>
         </is>
       </c>
       <c r="K155" s="10" t="inlineStr">
         <is>
-          <t>Named people</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L155" s="10" t="inlineStr">
         <is>
-          <t>L-09</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="M155" s="10" t="inlineStr">
         <is>
-          <t>1:1 with platform owner</t>
+          <t>HM OI-13</t>
         </is>
       </c>
       <c r="N155" s="15" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Open — BLOCKS BUILD</t>
         </is>
       </c>
     </row>
@@ -12080,32 +12104,32 @@
       </c>
       <c r="B156" s="12" t="inlineStr">
         <is>
-          <t>H-16</t>
+          <t>H-10</t>
         </is>
       </c>
       <c r="C156" s="12" t="inlineStr">
         <is>
-          <t>Forward the introduction</t>
+          <t>Send a welcome note</t>
         </is>
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>#/hm/intro</t>
+          <t>#/hm/welcome</t>
         </is>
       </c>
       <c r="E156" s="12" t="inlineStr">
         <is>
-          <t>Arrival</t>
+          <t>Recipient</t>
         </is>
       </c>
       <c r="F156" s="12" t="inlineStr">
         <is>
-          <t>Task appears only after the new hire consents</t>
+          <t>To — the new hire's personal email (read-only)</t>
         </is>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
-          <t>Task card</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H156" s="12" t="inlineStr">
@@ -12115,32 +12139,32 @@
       </c>
       <c r="I156" s="12" t="inlineStr">
         <is>
-          <t>New hire consent</t>
+          <t>Personal details task</t>
         </is>
       </c>
       <c r="J156" s="12" t="inlineStr">
         <is>
-          <t>No consent, no task — the gate is enforced across the join.</t>
+          <t>Depends on the new hire having supplied it.</t>
         </is>
       </c>
       <c r="K156" s="12" t="inlineStr">
         <is>
-          <t>NH introduction</t>
+          <t>NH personal details</t>
         </is>
       </c>
       <c r="L156" s="12" t="inlineStr">
         <is>
-          <t>L-02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M156" s="12" t="inlineStr">
         <is>
-          <t>No source — invented</t>
-        </is>
-      </c>
-      <c r="N156" s="15" t="inlineStr">
-        <is>
-          <t>Open — no source</t>
+          <t>HM Fields H-10.1</t>
+        </is>
+      </c>
+      <c r="N156" s="13" t="inlineStr">
+        <is>
+          <t>Aligned</t>
         </is>
       </c>
     </row>
@@ -12152,67 +12176,67 @@
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>H-16</t>
+          <t>H-10</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>Forward the introduction</t>
+          <t>Send a welcome note</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>#/hm/intro</t>
+          <t>#/hm/welcome</t>
         </is>
       </c>
       <c r="E157" s="10" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Body</t>
         </is>
       </c>
       <c r="F157" s="10" t="inlineStr">
         <is>
-          <t>What the new hire wrote, with their photo if shared</t>
+          <t>Standard welcome, pre-filled and editable</t>
         </is>
       </c>
       <c r="G157" s="10" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Rich text</t>
         </is>
       </c>
       <c r="H157" s="10" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr">
         <is>
-          <t>New hire task</t>
+          <t>Boilerplate</t>
         </is>
       </c>
       <c r="J157" s="10" t="inlineStr">
         <is>
-          <t>Read-only to the manager.</t>
+          <t>Written for the manager, not by them.</t>
         </is>
       </c>
       <c r="K157" s="10" t="inlineStr">
         <is>
-          <t>NH introduction</t>
+          <t>NH landing</t>
         </is>
       </c>
       <c r="L157" s="10" t="inlineStr">
         <is>
-          <t>L-02</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="M157" s="10" t="inlineStr">
         <is>
-          <t>No source — invented</t>
+          <t>HM Fields H-10.2</t>
         </is>
       </c>
       <c r="N157" s="15" t="inlineStr">
         <is>
-          <t>Open — no source</t>
+          <t>Open — see Alignment G-13</t>
         </is>
       </c>
     </row>
@@ -12224,62 +12248,62 @@
       </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
-          <t>H-16</t>
+          <t>H-10</t>
         </is>
       </c>
       <c r="C158" s="12" t="inlineStr">
         <is>
-          <t>Forward the introduction</t>
+          <t>Send a welcome note</t>
         </is>
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>#/hm/intro</t>
+          <t>#/hm/welcome</t>
         </is>
       </c>
       <c r="E158" s="12" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Body</t>
         </is>
       </c>
       <c r="F158" s="12" t="inlineStr">
         <is>
-          <t>Forward to the team</t>
+          <t>Your personal message</t>
         </is>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Multi line text</t>
         </is>
       </c>
       <c r="H158" s="12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="I158" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Blank</t>
         </is>
       </c>
       <c r="J158" s="12" t="inlineStr">
         <is>
-          <t>Explicit send. Nothing auto-posts.</t>
+          <t>The only part that genuinely needs the manager.</t>
         </is>
       </c>
       <c r="K158" s="12" t="inlineStr">
         <is>
-          <t>Team channel</t>
+          <t>NH landing</t>
         </is>
       </c>
       <c r="L158" s="12" t="inlineStr">
         <is>
-          <t>A-14 / L-02</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="M158" s="12" t="inlineStr">
         <is>
-          <t>NH OI-11</t>
+          <t>HM Fields H-10.3</t>
         </is>
       </c>
       <c r="N158" s="15" t="inlineStr">
@@ -12296,32 +12320,32 @@
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>H-16</t>
+          <t>H-10</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Forward the introduction</t>
+          <t>Send a welcome note</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>#/hm/intro</t>
+          <t>#/hm/welcome</t>
         </is>
       </c>
       <c r="E159" s="10" t="inlineStr">
         <is>
-          <t>Destination</t>
+          <t>System block</t>
         </is>
       </c>
       <c r="F159" s="10" t="inlineStr">
         <is>
-          <t>Where it goes: team channel, under the manager's name</t>
+          <t>'What to expect in your first week' — read-only</t>
         </is>
       </c>
       <c r="G159" s="10" t="inlineStr">
         <is>
-          <t>Display ×3</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H159" s="10" t="inlineStr">
@@ -12331,32 +12355,32 @@
       </c>
       <c r="I159" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>New hire's task list</t>
         </is>
       </c>
       <c r="J159" s="10" t="inlineStr">
         <is>
-          <t>New hire is told it was shared and when.</t>
+          <t>Generated, not written. Manager cannot edit it.</t>
         </is>
       </c>
       <c r="K159" s="10" t="inlineStr">
         <is>
-          <t>NH notification</t>
+          <t>NH task list</t>
         </is>
       </c>
       <c r="L159" s="10" t="inlineStr">
         <is>
-          <t>L-02</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="M159" s="10" t="inlineStr">
         <is>
-          <t>No source — invented</t>
+          <t>HM Fields H-10.4</t>
         </is>
       </c>
       <c r="N159" s="15" t="inlineStr">
         <is>
-          <t>Open — no source</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -12368,32 +12392,32 @@
       </c>
       <c r="B160" s="12" t="inlineStr">
         <is>
-          <t>H-SUB</t>
+          <t>H-10</t>
         </is>
       </c>
       <c r="C160" s="12" t="inlineStr">
         <is>
-          <t>The subtraction review</t>
+          <t>Send a welcome note</t>
         </is>
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>#/hm/subtraction</t>
+          <t>#/hm/welcome</t>
         </is>
       </c>
       <c r="E160" s="12" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Sequencing</t>
         </is>
       </c>
       <c r="F160" s="12" t="inlineStr">
         <is>
-          <t>19 manager tasks grouped by verdict, with conditions</t>
+          <t>Should land before the introduction is requested</t>
         </is>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
-          <t>Review screen</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H160" s="12" t="inlineStr">
@@ -12403,69 +12427,69 @@
       </c>
       <c r="I160" s="12" t="inlineStr">
         <is>
-          <t>HM Task Disposition</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J160" s="12" t="inlineStr">
         <is>
-          <t>Remove rows struck through. Six groups: remove, automate, exception-only, keep, undecided, adds work.</t>
+          <t>Stated, not enforced. Three welcome messages compete for the same week.</t>
         </is>
       </c>
       <c r="K160" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NH introduction</t>
         </is>
       </c>
       <c r="L160" s="12" t="inlineStr">
         <is>
-          <t>M-09 / M-11 / M-12</t>
+          <t>L-08</t>
         </is>
       </c>
       <c r="M160" s="12" t="inlineStr">
         <is>
-          <t>HM Task Disposition</t>
-        </is>
-      </c>
-      <c r="N160" s="11" t="inlineStr">
-        <is>
-          <t>Mockup device</t>
+          <t>Merge Analysis 7</t>
+        </is>
+      </c>
+      <c r="N160" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Hiring manager</t>
         </is>
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>HANDOFF</t>
+          <t>H-11</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>How the two portals connect</t>
+          <t>Name who they should meet</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>#/handoffs</t>
+          <t>#/hm/network</t>
         </is>
       </c>
       <c r="E161" s="10" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Framing</t>
         </is>
       </c>
       <c r="F161" s="10" t="inlineStr">
         <is>
-          <t>Nine handoffs with direction, live state and assumption</t>
+          <t>This adds to your workload — the only item that does</t>
         </is>
       </c>
       <c r="G161" s="10" t="inlineStr">
         <is>
-          <t>Review screen</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="H161" s="10" t="inlineStr">
@@ -12475,276 +12499,1428 @@
       </c>
       <c r="I161" s="10" t="inlineStr">
         <is>
-          <t>Computed</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J161" s="10" t="inlineStr">
         <is>
-          <t>Reads real state, so it shows what is wired right now. Buddy row flagged as a conflict.</t>
+          <t>Stated on the screen rather than hidden.</t>
         </is>
       </c>
       <c r="K161" s="10" t="inlineStr">
         <is>
-          <t>Both sides</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L161" s="10" t="inlineStr">
         <is>
-          <t>L-01…L-09</t>
+          <t>M-10</t>
         </is>
       </c>
       <c r="M161" s="10" t="inlineStr">
         <is>
-          <t>This alignment pass</t>
-        </is>
-      </c>
-      <c r="N161" s="11" t="inlineStr">
-        <is>
-          <t>Mockup device</t>
+          <t>HM OI-26</t>
+        </is>
+      </c>
+      <c r="N161" s="15" t="inlineStr">
+        <is>
+          <t>Open — needs decision</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="12" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Hiring manager</t>
         </is>
       </c>
       <c r="B162" s="12" t="inlineStr">
         <is>
-          <t>PROTO</t>
+          <t>H-11</t>
         </is>
       </c>
       <c r="C162" s="12" t="inlineStr">
         <is>
-          <t>Prototype controls</t>
+          <t>Name who they should meet</t>
         </is>
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>(bottom left)</t>
+          <t>#/hm/network</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Selection</t>
         </is>
       </c>
       <c r="F162" s="12" t="inlineStr">
         <is>
-          <t>Persona · country · runway · task-state scenario · buddy rule</t>
+          <t>Suggested people, pickable (7 in the pool)</t>
         </is>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
-          <t>Prototype control</t>
+          <t>Checkbox list</t>
         </is>
       </c>
       <c r="H162" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I162" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Org data</t>
         </is>
       </c>
       <c r="J162" s="12" t="inlineStr">
         <is>
-          <t>Clearly labelled as not product UI.</t>
+          <t>Five suggested with draft reasons; two unsuggested with none.</t>
         </is>
       </c>
       <c r="K162" s="12" t="inlineStr">
         <is>
-          <t>Both sides</t>
+          <t>NH network</t>
         </is>
       </c>
       <c r="L162" s="12" t="inlineStr">
         <is>
-          <t>A-45 / L-01</t>
+          <t>M-10</t>
         </is>
       </c>
       <c r="M162" s="12" t="inlineStr">
         <is>
-          <t>NH Stage 6</t>
-        </is>
-      </c>
-      <c r="N162" s="11" t="inlineStr">
-        <is>
-          <t>Mockup device</t>
+          <t>HM H-11</t>
+        </is>
+      </c>
+      <c r="N162" s="15" t="inlineStr">
+        <is>
+          <t>Open — see Alignment G-12</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="10" t="inlineStr">
         <is>
+          <t>Hiring manager</t>
+        </is>
+      </c>
+      <c r="B163" s="10" t="inlineStr">
+        <is>
+          <t>H-11</t>
+        </is>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
+        <is>
+          <t>Name who they should meet</t>
+        </is>
+      </c>
+      <c r="D163" s="10" t="inlineStr">
+        <is>
+          <t>#/hm/network</t>
+        </is>
+      </c>
+      <c r="E163" s="10" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="F163" s="10" t="inlineStr">
+        <is>
+          <t>Why should they meet this person? (required per person)</t>
+        </is>
+      </c>
+      <c r="G163" s="10" t="inlineStr">
+        <is>
+          <t>Multi line text</t>
+        </is>
+      </c>
+      <c r="H163" s="10" t="inlineStr">
+        <is>
+          <t>Yes per person</t>
+        </is>
+      </c>
+      <c r="I163" s="10" t="inlineStr">
+        <is>
+          <t>Draft text</t>
+        </is>
+      </c>
+      <c r="J163" s="10" t="inlineStr">
+        <is>
+          <t>Editable draft. Reaches the new hire verbatim.</t>
+        </is>
+      </c>
+      <c r="K163" s="10" t="inlineStr">
+        <is>
+          <t>NH network</t>
+        </is>
+      </c>
+      <c r="L163" s="10" t="inlineStr">
+        <is>
+          <t>L-06</t>
+        </is>
+      </c>
+      <c r="M163" s="10" t="inlineStr">
+        <is>
+          <t>1:1 with platform owner</t>
+        </is>
+      </c>
+      <c r="N163" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="12" t="inlineStr">
+        <is>
+          <t>Hiring manager</t>
+        </is>
+      </c>
+      <c r="B164" s="12" t="inlineStr">
+        <is>
+          <t>H-11</t>
+        </is>
+      </c>
+      <c r="C164" s="12" t="inlineStr">
+        <is>
+          <t>Name who they should meet</t>
+        </is>
+      </c>
+      <c r="D164" s="12" t="inlineStr">
+        <is>
+          <t>#/hm/network</t>
+        </is>
+      </c>
+      <c r="E164" s="12" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="F164" s="12" t="inlineStr">
+        <is>
+          <t>At least five people, each with a reason</t>
+        </is>
+      </c>
+      <c r="G164" s="12" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H164" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I164" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J164" s="12" t="inlineStr">
+        <is>
+          <t>Submit gated at five. Nobody has said what happens at three or twelve.</t>
+        </is>
+      </c>
+      <c r="K164" s="12" t="inlineStr">
+        <is>
+          <t>NH network</t>
+        </is>
+      </c>
+      <c r="L164" s="12" t="inlineStr">
+        <is>
+          <t>M-10</t>
+        </is>
+      </c>
+      <c r="M164" s="12" t="inlineStr">
+        <is>
+          <t>1:1 with platform owner</t>
+        </is>
+      </c>
+      <c r="N164" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="10" t="inlineStr">
+        <is>
+          <t>Hiring manager</t>
+        </is>
+      </c>
+      <c r="B165" s="10" t="inlineStr">
+        <is>
+          <t>H-11</t>
+        </is>
+      </c>
+      <c r="C165" s="10" t="inlineStr">
+        <is>
+          <t>Name who they should meet</t>
+        </is>
+      </c>
+      <c r="D165" s="10" t="inlineStr">
+        <is>
+          <t>#/hm/network</t>
+        </is>
+      </c>
+      <c r="E165" s="10" t="inlineStr">
+        <is>
+          <t>Notification</t>
+        </is>
+      </c>
+      <c r="F165" s="10" t="inlineStr">
+        <is>
+          <t>Each named person is notified</t>
+        </is>
+      </c>
+      <c r="G165" s="10" t="inlineStr">
+        <is>
+          <t>Behaviour</t>
+        </is>
+      </c>
+      <c r="H165" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I165" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J165" s="10" t="inlineStr">
+        <is>
+          <t>Shown as an effect; content of the notification not specified.</t>
+        </is>
+      </c>
+      <c r="K165" s="10" t="inlineStr">
+        <is>
+          <t>Named people</t>
+        </is>
+      </c>
+      <c r="L165" s="10" t="inlineStr">
+        <is>
+          <t>L-09</t>
+        </is>
+      </c>
+      <c r="M165" s="10" t="inlineStr">
+        <is>
+          <t>1:1 with platform owner</t>
+        </is>
+      </c>
+      <c r="N165" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="12" t="inlineStr">
+        <is>
+          <t>Hiring manager</t>
+        </is>
+      </c>
+      <c r="B166" s="12" t="inlineStr">
+        <is>
+          <t>H-16</t>
+        </is>
+      </c>
+      <c r="C166" s="12" t="inlineStr">
+        <is>
+          <t>Forward the introduction</t>
+        </is>
+      </c>
+      <c r="D166" s="12" t="inlineStr">
+        <is>
+          <t>#/hm/intro</t>
+        </is>
+      </c>
+      <c r="E166" s="12" t="inlineStr">
+        <is>
+          <t>Arrival</t>
+        </is>
+      </c>
+      <c r="F166" s="12" t="inlineStr">
+        <is>
+          <t>Task appears only after the new hire consents</t>
+        </is>
+      </c>
+      <c r="G166" s="12" t="inlineStr">
+        <is>
+          <t>Task card</t>
+        </is>
+      </c>
+      <c r="H166" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I166" s="12" t="inlineStr">
+        <is>
+          <t>New hire consent</t>
+        </is>
+      </c>
+      <c r="J166" s="12" t="inlineStr">
+        <is>
+          <t>No consent, no task — the gate is enforced across the join.</t>
+        </is>
+      </c>
+      <c r="K166" s="12" t="inlineStr">
+        <is>
+          <t>NH introduction</t>
+        </is>
+      </c>
+      <c r="L166" s="12" t="inlineStr">
+        <is>
+          <t>L-02</t>
+        </is>
+      </c>
+      <c r="M166" s="12" t="inlineStr">
+        <is>
+          <t>No source — invented</t>
+        </is>
+      </c>
+      <c r="N166" s="15" t="inlineStr">
+        <is>
+          <t>Open — no source</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="10" t="inlineStr">
+        <is>
+          <t>Hiring manager</t>
+        </is>
+      </c>
+      <c r="B167" s="10" t="inlineStr">
+        <is>
+          <t>H-16</t>
+        </is>
+      </c>
+      <c r="C167" s="10" t="inlineStr">
+        <is>
+          <t>Forward the introduction</t>
+        </is>
+      </c>
+      <c r="D167" s="10" t="inlineStr">
+        <is>
+          <t>#/hm/intro</t>
+        </is>
+      </c>
+      <c r="E167" s="10" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="F167" s="10" t="inlineStr">
+        <is>
+          <t>What the new hire wrote, with their photo if shared</t>
+        </is>
+      </c>
+      <c r="G167" s="10" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="H167" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I167" s="10" t="inlineStr">
+        <is>
+          <t>New hire task</t>
+        </is>
+      </c>
+      <c r="J167" s="10" t="inlineStr">
+        <is>
+          <t>Read-only to the manager.</t>
+        </is>
+      </c>
+      <c r="K167" s="10" t="inlineStr">
+        <is>
+          <t>NH introduction</t>
+        </is>
+      </c>
+      <c r="L167" s="10" t="inlineStr">
+        <is>
+          <t>L-02</t>
+        </is>
+      </c>
+      <c r="M167" s="10" t="inlineStr">
+        <is>
+          <t>No source — invented</t>
+        </is>
+      </c>
+      <c r="N167" s="15" t="inlineStr">
+        <is>
+          <t>Open — no source</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="12" t="inlineStr">
+        <is>
+          <t>Hiring manager</t>
+        </is>
+      </c>
+      <c r="B168" s="12" t="inlineStr">
+        <is>
+          <t>H-16</t>
+        </is>
+      </c>
+      <c r="C168" s="12" t="inlineStr">
+        <is>
+          <t>Forward the introduction</t>
+        </is>
+      </c>
+      <c r="D168" s="12" t="inlineStr">
+        <is>
+          <t>#/hm/intro</t>
+        </is>
+      </c>
+      <c r="E168" s="12" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="F168" s="12" t="inlineStr">
+        <is>
+          <t>Forward to the team</t>
+        </is>
+      </c>
+      <c r="G168" s="12" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H168" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I168" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J168" s="12" t="inlineStr">
+        <is>
+          <t>Explicit send. Nothing auto-posts.</t>
+        </is>
+      </c>
+      <c r="K168" s="12" t="inlineStr">
+        <is>
+          <t>Team channel</t>
+        </is>
+      </c>
+      <c r="L168" s="12" t="inlineStr">
+        <is>
+          <t>A-14 / L-02</t>
+        </is>
+      </c>
+      <c r="M168" s="12" t="inlineStr">
+        <is>
+          <t>NH OI-11</t>
+        </is>
+      </c>
+      <c r="N168" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="10" t="inlineStr">
+        <is>
+          <t>Hiring manager</t>
+        </is>
+      </c>
+      <c r="B169" s="10" t="inlineStr">
+        <is>
+          <t>H-16</t>
+        </is>
+      </c>
+      <c r="C169" s="10" t="inlineStr">
+        <is>
+          <t>Forward the introduction</t>
+        </is>
+      </c>
+      <c r="D169" s="10" t="inlineStr">
+        <is>
+          <t>#/hm/intro</t>
+        </is>
+      </c>
+      <c r="E169" s="10" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+      <c r="F169" s="10" t="inlineStr">
+        <is>
+          <t>Where it goes: team channel, under the manager's name</t>
+        </is>
+      </c>
+      <c r="G169" s="10" t="inlineStr">
+        <is>
+          <t>Display ×3</t>
+        </is>
+      </c>
+      <c r="H169" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I169" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J169" s="10" t="inlineStr">
+        <is>
+          <t>New hire is told it was shared and when.</t>
+        </is>
+      </c>
+      <c r="K169" s="10" t="inlineStr">
+        <is>
+          <t>NH notification</t>
+        </is>
+      </c>
+      <c r="L169" s="10" t="inlineStr">
+        <is>
+          <t>L-02</t>
+        </is>
+      </c>
+      <c r="M169" s="10" t="inlineStr">
+        <is>
+          <t>No source — invented</t>
+        </is>
+      </c>
+      <c r="N169" s="15" t="inlineStr">
+        <is>
+          <t>Open — no source</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="12" t="inlineStr">
+        <is>
+          <t>Hiring manager</t>
+        </is>
+      </c>
+      <c r="B170" s="12" t="inlineStr">
+        <is>
+          <t>H-06</t>
+        </is>
+      </c>
+      <c r="C170" s="12" t="inlineStr">
+        <is>
+          <t>Corporate card</t>
+        </is>
+      </c>
+      <c r="D170" s="12" t="inlineStr">
+        <is>
+          <t>#/hm/card</t>
+        </is>
+      </c>
+      <c r="E170" s="12" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F170" s="12" t="inlineStr">
+        <is>
+          <t>Will they travel on behalf of Equinix and need a card?</t>
+        </is>
+      </c>
+      <c r="G170" s="12" t="inlineStr">
+        <is>
+          <t>Radio</t>
+        </is>
+      </c>
+      <c r="H170" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I170" s="12" t="inlineStr">
+        <is>
+          <t>Blank</t>
+        </is>
+      </c>
+      <c r="J170" s="12" t="inlineStr">
+        <is>
+          <t>Framed around travel, not entitlement. One tap.</t>
+        </is>
+      </c>
+      <c r="K170" s="12" t="inlineStr">
+        <is>
+          <t>NH Day 2 card</t>
+        </is>
+      </c>
+      <c r="L170" s="12" t="inlineStr">
+        <is>
+          <t>M-19</t>
+        </is>
+      </c>
+      <c r="M170" s="12" t="inlineStr">
+        <is>
+          <t>PRD v1.4</t>
+        </is>
+      </c>
+      <c r="N170" s="14" t="inlineStr">
+        <is>
+          <t>Gap closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="10" t="inlineStr">
+        <is>
+          <t>Hiring manager</t>
+        </is>
+      </c>
+      <c r="B171" s="10" t="inlineStr">
+        <is>
+          <t>H-06</t>
+        </is>
+      </c>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>Corporate card</t>
+        </is>
+      </c>
+      <c r="D171" s="10" t="inlineStr">
+        <is>
+          <t>#/hm/card</t>
+        </is>
+      </c>
+      <c r="E171" s="10" t="inlineStr">
+        <is>
+          <t>Consequence</t>
+        </is>
+      </c>
+      <c r="F171" s="10" t="inlineStr">
+        <is>
+          <t>What your yes sets off — four steps to the card provider</t>
+        </is>
+      </c>
+      <c r="G171" s="10" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="H171" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I171" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J171" s="10" t="inlineStr">
+        <is>
+          <t>Agreement on Day 2, weekly extract to Accounts Payable, provider issues the link.</t>
+        </is>
+      </c>
+      <c r="K171" s="10" t="inlineStr">
+        <is>
+          <t>NH Day 2 card</t>
+        </is>
+      </c>
+      <c r="L171" s="10" t="inlineStr">
+        <is>
+          <t>L-10</t>
+        </is>
+      </c>
+      <c r="M171" s="10" t="inlineStr">
+        <is>
+          <t>PRD v1.4</t>
+        </is>
+      </c>
+      <c r="N171" s="14" t="inlineStr">
+        <is>
+          <t>Gap closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="12" t="inlineStr">
+        <is>
+          <t>Hiring manager</t>
+        </is>
+      </c>
+      <c r="B172" s="12" t="inlineStr">
+        <is>
+          <t>H-06</t>
+        </is>
+      </c>
+      <c r="C172" s="12" t="inlineStr">
+        <is>
+          <t>Corporate card</t>
+        </is>
+      </c>
+      <c r="D172" s="12" t="inlineStr">
+        <is>
+          <t>#/hm/card</t>
+        </is>
+      </c>
+      <c r="E172" s="12" t="inlineStr">
+        <is>
+          <t>Consequence</t>
+        </is>
+      </c>
+      <c r="F172" s="12" t="inlineStr">
+        <is>
+          <t>A no creates nothing, and the new hire never sees the subject</t>
+        </is>
+      </c>
+      <c r="G172" s="12" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="H172" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I172" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J172" s="12" t="inlineStr">
+        <is>
+          <t>The negative answer is a designed outcome, not an absence.</t>
+        </is>
+      </c>
+      <c r="K172" s="12" t="inlineStr">
+        <is>
+          <t>NH landing</t>
+        </is>
+      </c>
+      <c r="L172" s="12" t="inlineStr">
+        <is>
+          <t>L-10</t>
+        </is>
+      </c>
+      <c r="M172" s="12" t="inlineStr">
+        <is>
+          <t>PRD v1.4</t>
+        </is>
+      </c>
+      <c r="N172" s="14" t="inlineStr">
+        <is>
+          <t>Gap closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="10" t="inlineStr">
+        <is>
+          <t>Hiring manager</t>
+        </is>
+      </c>
+      <c r="B173" s="10" t="inlineStr">
+        <is>
+          <t>H-06</t>
+        </is>
+      </c>
+      <c r="C173" s="10" t="inlineStr">
+        <is>
+          <t>Corporate card</t>
+        </is>
+      </c>
+      <c r="D173" s="10" t="inlineStr">
+        <is>
+          <t>#/hm/card</t>
+        </is>
+      </c>
+      <c r="E173" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F173" s="10" t="inlineStr">
+        <is>
+          <t>Task name in the portal; cost centre and approver</t>
+        </is>
+      </c>
+      <c r="G173" s="10" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="H173" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I173" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J173" s="10" t="inlineStr">
+        <is>
+          <t>Two details the requirement itself leaves open.</t>
+        </is>
+      </c>
+      <c r="K173" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L173" s="10" t="inlineStr">
+        <is>
+          <t>M-19</t>
+        </is>
+      </c>
+      <c r="M173" s="10" t="inlineStr">
+        <is>
+          <t>PRD v1.4</t>
+        </is>
+      </c>
+      <c r="N173" s="15" t="inlineStr">
+        <is>
+          <t>Open — content needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="12" t="inlineStr">
+        <is>
+          <t>Hiring manager</t>
+        </is>
+      </c>
+      <c r="B174" s="12" t="inlineStr">
+        <is>
+          <t>H-11</t>
+        </is>
+      </c>
+      <c r="C174" s="12" t="inlineStr">
+        <is>
+          <t>Name who they should meet</t>
+        </is>
+      </c>
+      <c r="D174" s="12" t="inlineStr">
+        <is>
+          <t>#/hm/network</t>
+        </is>
+      </c>
+      <c r="E174" s="12" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="F174" s="12" t="inlineStr">
+        <is>
+          <t>Notice: this capability may already exist natively</t>
+        </is>
+      </c>
+      <c r="G174" s="12" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="H174" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I174" s="12" t="inlineStr">
+        <is>
+          <t>Workday deck</t>
+        </is>
+      </c>
+      <c r="J174" s="12" t="inlineStr">
+        <is>
+          <t>Flags that the platform ships people-to-meet and helpful-contacts already.</t>
+        </is>
+      </c>
+      <c r="K174" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L174" s="12" t="inlineStr">
+        <is>
+          <t>M-21</t>
+        </is>
+      </c>
+      <c r="M174" s="12" t="inlineStr">
+        <is>
+          <t>Onboarding Workday deck</t>
+        </is>
+      </c>
+      <c r="N174" s="15" t="inlineStr">
+        <is>
+          <t>Open — BLOCKS BUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="10" t="inlineStr">
+        <is>
+          <t>Hiring manager</t>
+        </is>
+      </c>
+      <c r="B175" s="10" t="inlineStr">
+        <is>
+          <t>H-10</t>
+        </is>
+      </c>
+      <c r="C175" s="10" t="inlineStr">
+        <is>
+          <t>Send a welcome note</t>
+        </is>
+      </c>
+      <c r="D175" s="10" t="inlineStr">
+        <is>
+          <t>#/hm/welcome</t>
+        </is>
+      </c>
+      <c r="E175" s="10" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="F175" s="10" t="inlineStr">
+        <is>
+          <t>Notice: welcome memo may already exist natively</t>
+        </is>
+      </c>
+      <c r="G175" s="10" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="H175" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I175" s="10" t="inlineStr">
+        <is>
+          <t>Workday deck</t>
+        </is>
+      </c>
+      <c r="J175" s="10" t="inlineStr">
+        <is>
+          <t>Only the generated first-week block is clearly additive.</t>
+        </is>
+      </c>
+      <c r="K175" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L175" s="10" t="inlineStr">
+        <is>
+          <t>M-21</t>
+        </is>
+      </c>
+      <c r="M175" s="10" t="inlineStr">
+        <is>
+          <t>Onboarding Workday deck</t>
+        </is>
+      </c>
+      <c r="N175" s="15" t="inlineStr">
+        <is>
+          <t>Open — BLOCKS BUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="12" t="inlineStr">
+        <is>
+          <t>Hiring manager</t>
+        </is>
+      </c>
+      <c r="B176" s="12" t="inlineStr">
+        <is>
+          <t>H-SUB</t>
+        </is>
+      </c>
+      <c r="C176" s="12" t="inlineStr">
+        <is>
+          <t>The subtraction review</t>
+        </is>
+      </c>
+      <c r="D176" s="12" t="inlineStr">
+        <is>
+          <t>#/hm/subtraction</t>
+        </is>
+      </c>
+      <c r="E176" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F176" s="12" t="inlineStr">
+        <is>
+          <t>19 manager tasks grouped by verdict, with conditions</t>
+        </is>
+      </c>
+      <c r="G176" s="12" t="inlineStr">
+        <is>
+          <t>Review screen</t>
+        </is>
+      </c>
+      <c r="H176" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I176" s="12" t="inlineStr">
+        <is>
+          <t>HM Task Disposition</t>
+        </is>
+      </c>
+      <c r="J176" s="12" t="inlineStr">
+        <is>
+          <t>Remove rows struck through. Six groups: remove, automate, exception-only, keep, undecided, adds work.</t>
+        </is>
+      </c>
+      <c r="K176" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L176" s="12" t="inlineStr">
+        <is>
+          <t>M-09 / M-11 / M-12</t>
+        </is>
+      </c>
+      <c r="M176" s="12" t="inlineStr">
+        <is>
+          <t>HM Task Disposition</t>
+        </is>
+      </c>
+      <c r="N176" s="11" t="inlineStr">
+        <is>
+          <t>Mockup device</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="10" t="inlineStr">
+        <is>
           <t>Shared</t>
         </is>
       </c>
-      <c r="B163" s="10" t="inlineStr">
+      <c r="B177" s="10" t="inlineStr">
+        <is>
+          <t>HANDOFF</t>
+        </is>
+      </c>
+      <c r="C177" s="10" t="inlineStr">
+        <is>
+          <t>How the two portals connect</t>
+        </is>
+      </c>
+      <c r="D177" s="10" t="inlineStr">
+        <is>
+          <t>#/handoffs</t>
+        </is>
+      </c>
+      <c r="E177" s="10" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F177" s="10" t="inlineStr">
+        <is>
+          <t>Eleven handoffs with direction, live state and assumption</t>
+        </is>
+      </c>
+      <c r="G177" s="10" t="inlineStr">
+        <is>
+          <t>Review screen</t>
+        </is>
+      </c>
+      <c r="H177" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I177" s="10" t="inlineStr">
+        <is>
+          <t>Computed</t>
+        </is>
+      </c>
+      <c r="J177" s="10" t="inlineStr">
+        <is>
+          <t>Reads real state, so it shows what is wired right now. Buddy row flagged as a conflict.</t>
+        </is>
+      </c>
+      <c r="K177" s="10" t="inlineStr">
+        <is>
+          <t>Both sides</t>
+        </is>
+      </c>
+      <c r="L177" s="10" t="inlineStr">
+        <is>
+          <t>L-01…L-09</t>
+        </is>
+      </c>
+      <c r="M177" s="10" t="inlineStr">
+        <is>
+          <t>This alignment pass</t>
+        </is>
+      </c>
+      <c r="N177" s="11" t="inlineStr">
+        <is>
+          <t>Mockup device</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="12" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="B178" s="12" t="inlineStr">
         <is>
           <t>PROTO</t>
         </is>
       </c>
-      <c r="C163" s="10" t="inlineStr">
+      <c r="C178" s="12" t="inlineStr">
+        <is>
+          <t>Prototype controls</t>
+        </is>
+      </c>
+      <c r="D178" s="12" t="inlineStr">
+        <is>
+          <t>(bottom left)</t>
+        </is>
+      </c>
+      <c r="E178" s="12" t="inlineStr">
+        <is>
+          <t>Controls</t>
+        </is>
+      </c>
+      <c r="F178" s="12" t="inlineStr">
+        <is>
+          <t>Persona · country · runway · task-state scenario · buddy rule</t>
+        </is>
+      </c>
+      <c r="G178" s="12" t="inlineStr">
+        <is>
+          <t>Prototype control</t>
+        </is>
+      </c>
+      <c r="H178" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I178" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J178" s="12" t="inlineStr">
+        <is>
+          <t>Clearly labelled as not product UI.</t>
+        </is>
+      </c>
+      <c r="K178" s="12" t="inlineStr">
+        <is>
+          <t>Both sides</t>
+        </is>
+      </c>
+      <c r="L178" s="12" t="inlineStr">
+        <is>
+          <t>A-45 / L-01</t>
+        </is>
+      </c>
+      <c r="M178" s="12" t="inlineStr">
+        <is>
+          <t>NH Stage 6</t>
+        </is>
+      </c>
+      <c r="N178" s="11" t="inlineStr">
+        <is>
+          <t>Mockup device</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="10" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="B179" s="10" t="inlineStr">
+        <is>
+          <t>PROTO</t>
+        </is>
+      </c>
+      <c r="C179" s="10" t="inlineStr">
         <is>
           <t>Assumptions &amp; gaps panel</t>
         </is>
       </c>
-      <c r="D163" s="10" t="inlineStr">
+      <c r="D179" s="10" t="inlineStr">
         <is>
           <t>(ribbon)</t>
         </is>
       </c>
-      <c r="E163" s="10" t="inlineStr">
+      <c r="E179" s="10" t="inlineStr">
         <is>
           <t>Panel</t>
         </is>
       </c>
-      <c r="F163" s="10" t="inlineStr">
-        <is>
-          <t>74 entries, filterable by side, with provenance tags</t>
-        </is>
-      </c>
-      <c r="G163" s="10" t="inlineStr">
+      <c r="F179" s="10" t="inlineStr">
+        <is>
+          <t>82 entries, filterable by side, with provenance tags</t>
+        </is>
+      </c>
+      <c r="G179" s="10" t="inlineStr">
         <is>
           <t>Panel</t>
         </is>
       </c>
-      <c r="H163" s="10" t="inlineStr">
+      <c r="H179" s="10" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I163" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J163" s="10" t="inlineStr">
-        <is>
-          <t>47 new hire · 18 manager · 9 connection. Markers on screen link into it.</t>
-        </is>
-      </c>
-      <c r="K163" s="10" t="inlineStr">
+      <c r="I179" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J179" s="10" t="inlineStr">
+        <is>
+          <t>50 new hire · 21 manager · 11 connection; 2 retired. Six provenance tags.</t>
+        </is>
+      </c>
+      <c r="K179" s="10" t="inlineStr">
         <is>
           <t>Both sides</t>
         </is>
       </c>
-      <c r="L163" s="10" t="inlineStr">
+      <c r="L179" s="10" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="M163" s="10" t="inlineStr">
+      <c r="M179" s="10" t="inlineStr">
         <is>
           <t>NH + HM specs</t>
         </is>
       </c>
-      <c r="N163" s="11" t="inlineStr">
+      <c r="N179" s="11" t="inlineStr">
         <is>
           <t>Mockup device</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="17" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="17" t="inlineStr">
         <is>
           <t>COUNTS</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="18" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="18" t="inlineStr">
         <is>
           <t>Elements mapped</t>
         </is>
       </c>
-      <c r="B166" s="19">
-        <f>COUNTA(F5:F163)</f>
+      <c r="B182" s="19">
+        <f>COUNTA(F5:F179)</f>
         <v/>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="18" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="18" t="inlineStr">
         <is>
           <t>New hire side</t>
         </is>
       </c>
-      <c r="B167" s="19">
-        <f>COUNTIF(A5:A163,"New hire")</f>
+      <c r="B183" s="19">
+        <f>COUNTIF(A5:A179,"New hire")</f>
         <v/>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="18" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="18" t="inlineStr">
         <is>
           <t>Hiring manager side</t>
         </is>
       </c>
-      <c r="B168" s="19">
-        <f>COUNTIF(A5:A163,"Hiring manager")</f>
+      <c r="B184" s="19">
+        <f>COUNTIF(A5:A179,"Hiring manager")</f>
         <v/>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="18" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="18" t="inlineStr">
         <is>
           <t>Elements with a cross-portal link</t>
         </is>
       </c>
-      <c r="B169" s="19">
-        <f>COUNTIFS(K5:K163,"&lt;&gt;—",K5:K163,"&lt;&gt;")</f>
+      <c r="B185" s="19">
+        <f>COUNTIFS(K5:K179,"&lt;&gt;—",K5:K179,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="18" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="18" t="inlineStr">
         <is>
           <t>Aligned</t>
         </is>
       </c>
-      <c r="B170" s="19">
-        <f>COUNTIF(N5:N163,"Aligned")</f>
+      <c r="B186" s="19">
+        <f>COUNTIF(N5:N179,"Aligned")</f>
         <v/>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="18" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="18" t="inlineStr">
         <is>
           <t>Gap closed</t>
         </is>
       </c>
-      <c r="B171" s="19">
-        <f>COUNTIF(N5:N163,"Gap closed*")</f>
+      <c r="B187" s="19">
+        <f>COUNTIF(N5:N179,"Gap closed*")</f>
         <v/>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="18" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="18" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="B172" s="19">
-        <f>COUNTIF(N5:N163,"Open*")</f>
+      <c r="B188" s="19">
+        <f>COUNTIF(N5:N179,"Open*")</f>
         <v/>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="18" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="18" t="inlineStr">
         <is>
           <t>Conflict</t>
         </is>
       </c>
-      <c r="B173" s="19">
-        <f>COUNTIF(N5:N163,"CONFLICT*")</f>
+      <c r="B189" s="19">
+        <f>COUNTIF(N5:N179,"CONFLICT*")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N163"/>
+  <autoFilter ref="A4:N179"/>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
@@ -12758,7 +13934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12771,6 +13947,7 @@
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="58" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12783,7 +13960,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>One row per finding. Sort by Priority for the working list. Six rows block build. Four are conflicts between sources, which are the expensive ones because both readings are currently being designed towards.</t>
+          <t>One row per finding. Sort by Priority for the working list. Six rows block build. Four are conflicts between sources, which are the expensive ones because both readings are currently being designed towards. The last column records what the mockups were changed to do about each one.</t>
         </is>
       </c>
     </row>
@@ -12838,6 +14015,11 @@
           <t>Priority</t>
         </is>
       </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>Closed in the mockup?</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -12890,6 +14072,11 @@
           <t>1 — Blocks build</t>
         </is>
       </c>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>YES — the real US pack (28 documents) and the whole-process figure (416 instances) now appear on the policies screen, flagged as true-today-not-right. The decision itself is still yours.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -12942,6 +14129,11 @@
           <t>1 — Blocks build</t>
         </is>
       </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>YES — document language is now derived from country and stated on screen; the Tab 3 field is demoted to communications only. A-03 rewritten.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -12989,9 +14181,14 @@
           <t>PEX</t>
         </is>
       </c>
-      <c r="J7" s="20" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>4 — Monitor</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>n/a — already aligned.</t>
         </is>
       </c>
     </row>
@@ -13046,6 +14243,11 @@
           <t>1 — Blocks build</t>
         </is>
       </c>
+      <c r="K8" s="22" t="inlineStr">
+        <is>
+          <t>NO — an architecture decision, not a mockup change. The inline-versus-link-out split stays visible on screen.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -13093,9 +14295,14 @@
           <t>Benefits COE / DIO</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t>3 — Content</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>YES — the benefits card now says it waits on the employee number, not only on a date.</t>
         </is>
       </c>
     </row>
@@ -13130,7 +14337,7 @@
           <t>Now fully specified. A pre-start manager task: 'New hire will travel on behalf of Equinix and be provided a corporate card' — yes/no. If yes, conditional logic creates a task for the new hire on Day 2 (post start date): PDF review plus e-signature. A weekly extract of completed agreements goes to Accounts Payable, who submit to Citi; Citi then sends an individualised application link. Extract fields: first name, last name, email, cost centre, country, EQXID, employee number, shipping address. Contingent workers out of scope. Citi cannot host the agreement, so it lives in Workday and/or ServiceNow.</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="24" t="inlineStr">
         <is>
           <t>SUPERSEDED</t>
         </is>
@@ -13148,6 +14355,11 @@
       <c r="J10" s="15" t="inlineStr">
         <is>
           <t>2 — Build now</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>YES — built on both sides. Manager yes/no framed around travel; the new hire sees a Day 2 item only when the answer is yes. M-12 retired; M-19 and L-10 added.</t>
         </is>
       </c>
     </row>
@@ -13182,7 +14394,7 @@
           <t>New requirement: the Workday scrum team is building mandatory fields required for the ADP payroll integration, to be surfaced through 'a new, globally universal form in the preboarding SNOW portal experience'. An 80/20 split — core universal fields for 80% of hires, conditional logic for local compliance fields for the remaining 20%. Expected Q3 and explicitly in scope for this PRD.</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>NEW REQUIREMENT</t>
         </is>
@@ -13200,6 +14412,11 @@
       <c r="J11" s="16" t="inlineStr">
         <is>
           <t>1 — Blocks build</t>
+        </is>
+      </c>
+      <c r="K11" s="25" t="inlineStr">
+        <is>
+          <t>PARTLY — the wizard is unchanged and remains the vehicle. It cannot be reconciled until the mandatory-field list lands.</t>
         </is>
       </c>
     </row>
@@ -13254,6 +14471,11 @@
           <t>2 — Build now</t>
         </is>
       </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>NO — needs the document-sequencing decision. Still flagged on screen as a proposal.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -13306,6 +14528,11 @@
           <t>2 — Build now</t>
         </is>
       </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>YES — carousel built above the progress tracker, rail link kept. A-35 rewritten as answered.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -13353,9 +14580,14 @@
           <t>DIO</t>
         </is>
       </c>
-      <c r="J14" s="20" t="inlineStr">
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t>4 — Monitor</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>n/a — already aligned.</t>
         </is>
       </c>
     </row>
@@ -13410,6 +14642,11 @@
           <t>1 — Blocks build</t>
         </is>
       </c>
+      <c r="K15" s="20" t="inlineStr">
+        <is>
+          <t>ALREADY — both rules implemented with a switch. The underlying conflict is still unresolved.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -13462,6 +14699,11 @@
           <t>2 — Build now</t>
         </is>
       </c>
+      <c r="K16" s="25" t="inlineStr">
+        <is>
+          <t>PARTLY — the native-capability question is now on the screen itself (M-21). The build decision is still open.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -13509,9 +14751,14 @@
           <t>DIO / PEX</t>
         </is>
       </c>
-      <c r="J17" s="21" t="inlineStr">
+      <c r="J17" s="23" t="inlineStr">
         <is>
           <t>3 — Content</t>
+        </is>
+      </c>
+      <c r="K17" s="25" t="inlineStr">
+        <is>
+          <t>PARTLY — the same note added to the welcome screen (M-21).</t>
         </is>
       </c>
     </row>
@@ -13566,6 +14813,11 @@
           <t>2 — Build now</t>
         </is>
       </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>YES — proxy reframed as a standing capability for managers and People Experience, not Day 1 cover. M-20 added.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -13613,9 +14865,14 @@
           <t>PEX</t>
         </is>
       </c>
-      <c r="J19" s="21" t="inlineStr">
+      <c r="J19" s="23" t="inlineStr">
         <is>
           <t>3 — Content</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>YES — the buddy is now described as covering the first three months and beyond.</t>
         </is>
       </c>
     </row>
@@ -13670,6 +14927,11 @@
           <t>2 — Build now</t>
         </is>
       </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>YES — the three-way disagreement is now stated on the credentials card itself.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -13717,9 +14979,14 @@
           <t>EUT</t>
         </is>
       </c>
-      <c r="J21" s="20" t="inlineStr">
+      <c r="J21" s="21" t="inlineStr">
         <is>
           <t>4 — Monitor</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>n/a — already aligned.</t>
         </is>
       </c>
     </row>
@@ -13774,6 +15041,11 @@
           <t>2 — Build now</t>
         </is>
       </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>NO — a workbook correction, not a mockup change.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -13826,6 +15098,11 @@
           <t>2 — Build now</t>
         </is>
       </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>NO — the third portal is not built. Out of scope for this pass.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -13873,9 +15150,14 @@
           <t>CRE / IBX / PEX</t>
         </is>
       </c>
-      <c r="J24" s="21" t="inlineStr">
+      <c r="J24" s="23" t="inlineStr">
         <is>
           <t>3 — Content</t>
+        </is>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>NO — needs a decision on whether swag belongs in the portal at all.</t>
         </is>
       </c>
     </row>
@@ -13930,6 +15212,11 @@
           <t>2 — Build now</t>
         </is>
       </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>YES — built as a required task with a change-request path. A-49 and L-11 added.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -13982,6 +15269,11 @@
           <t>2 — Build now</t>
         </is>
       </c>
+      <c r="K26" s="20" t="inlineStr">
+        <is>
+          <t>YES — built as a launchable task; the old passive card is gone. A-50 added.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
@@ -14029,9 +15321,14 @@
           <t>PEX / CRE</t>
         </is>
       </c>
-      <c r="J27" s="20" t="inlineStr">
+      <c r="J27" s="21" t="inlineStr">
         <is>
           <t>4 — Monitor</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>n/a — already aligned.</t>
         </is>
       </c>
     </row>
@@ -14086,6 +15383,11 @@
           <t>2 — Build now</t>
         </is>
       </c>
+      <c r="K28" s="20" t="inlineStr">
+        <is>
+          <t>YES — the 25 state addenda are named on screen, with the point that 24 of them do not apply.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -14133,9 +15435,14 @@
           <t>Legal / PEX</t>
         </is>
       </c>
-      <c r="J29" s="21" t="inlineStr">
+      <c r="J29" s="23" t="inlineStr">
         <is>
           <t>3 — Content</t>
+        </is>
+      </c>
+      <c r="K29" s="22" t="inlineStr">
+        <is>
+          <t>NO — Poland is not a country option in the mockup. The whole-process figure is shown instead.</t>
         </is>
       </c>
     </row>
@@ -14223,8 +15530,41 @@
         <v/>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>Closed in the mockup</t>
+        </is>
+      </c>
+      <c r="B39" s="19">
+        <f>COUNTIF(K5:K29,"YES*")+COUNTIF(K5:K29,"ALREADY*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>Partly closed</t>
+        </is>
+      </c>
+      <c r="B40" s="19">
+        <f>COUNTIF(K5:K29,"PARTLY*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>Not a mockup change</t>
+        </is>
+      </c>
+      <c r="B41" s="19">
+        <f>COUNTIF(K5:K29,"NO*")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:J29"/>
+  <autoFilter ref="A4:K29"/>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
@@ -14550,12 +15890,12 @@
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>Yes — but language is driven by a user preference, not by country</t>
+          <t>Yes — served in the language required for the country of hire</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>CONFLICT — see G-02. Change the language mechanism to country-derived.</t>
+          <t>CLOSED in the mockup. Language is now derived from country and stated on screen; the preference field covers communications only.</t>
         </is>
       </c>
     </row>
@@ -14674,14 +16014,14 @@
           <t>Country-appropriate handbook as reference. Key policies acknowledged separately as universal tasks.</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr">
-        <is>
-          <t>Partly — one country handbook shown as reference material</t>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Yes — with its real size and the problem named</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>GAP — see G-24. Every US hire receives all 25 state addenda regardless of work state.</t>
+          <t>The mockup now shows the full 28-document bundle and flags that 24 of the 25 state addenda do not apply. The decision on what survives is still open (G-01).</t>
         </is>
       </c>
     </row>
@@ -14765,7 +16105,7 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Add the Workday employee-ID dependency to the disabled state (G-05).</t>
+          <t>CLOSED in the mockup — the card now says it waits on the employee number, not only on a date.</t>
         </is>
       </c>
     </row>
@@ -15052,14 +16392,14 @@
           <t>Manager yes/no pre-start; new hire PDF review plus e-signature on Day 2; weekly extract to Accounts Payable, then Citi issues the application link.</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>No — currently listed as Undecided and not built</t>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Yes — built on both sides</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>SUPERSEDED — build it (G-06). Note it is Day 2, not pre-Day 1.</t>
+          <t>CLOSED. Manager yes/no framed around travel; the new hire sees a Day 2 item only when the answer is yes. Open: the task's final name, and whether cost centre and approver are captured.</t>
         </is>
       </c>
     </row>
